--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF064698-A154-4B25-BE65-5FA2D3540356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED49FD0A-2C9F-4B91-B615-0332AE7669B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
   <si>
     <t>Value</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t>capacity_scrap_total</t>
+  </si>
+  <si>
+    <t>total_facility_cap_initial</t>
   </si>
 </sst>
 </file>
@@ -860,7 +863,7 @@
         <v>414000</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F2">
         <v>1775265.6417320003</v>
@@ -896,7 +899,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -913,7 +916,7 @@
         <v>414000</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F3">
         <v>1722922.372057667</v>
@@ -949,7 +952,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -966,7 +969,7 @@
         <v>414000</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F4">
         <v>1670579.1023833335</v>
@@ -1002,7 +1005,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
@@ -1019,7 +1022,7 @@
         <v>414000</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F5">
         <v>1618235.832709</v>
@@ -1055,7 +1058,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -1072,7 +1075,7 @@
         <v>414000</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F6">
         <v>1565892.5630346665</v>
@@ -1108,7 +1111,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -1125,7 +1128,7 @@
         <v>414000</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F7">
         <v>1513549.293360333</v>
@@ -1161,7 +1164,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -1178,7 +1181,7 @@
         <v>414000</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F8">
         <v>1461206.0236859999</v>
@@ -1214,7 +1217,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -1231,7 +1234,7 @@
         <v>414000</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F9">
         <v>1444015.15599508</v>
@@ -1267,7 +1270,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -1284,7 +1287,7 @@
         <v>414000</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F10">
         <v>1426824.2883041599</v>
@@ -1320,7 +1323,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -1337,7 +1340,7 @@
         <v>414000</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F11">
         <v>1409633.42061324</v>
@@ -1373,7 +1376,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -1390,7 +1393,7 @@
         <v>414000</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F12">
         <v>1392442.5529223196</v>
@@ -1426,7 +1429,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -1443,7 +1446,7 @@
         <v>414000</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F13">
         <v>1375251.6852313997</v>
@@ -1479,7 +1482,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
@@ -1496,7 +1499,7 @@
         <v>414000</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F14">
         <v>1358060.8175404796</v>
@@ -1532,7 +1535,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -1549,7 +1552,7 @@
         <v>414000</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F15">
         <v>1340869.9498495597</v>
@@ -1585,7 +1588,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -1602,7 +1605,7 @@
         <v>414000</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F16">
         <v>1323679.0821586396</v>
@@ -1638,7 +1641,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q16">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
@@ -1655,7 +1658,7 @@
         <v>414000</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F17">
         <v>1306488.2144677194</v>
@@ -1691,7 +1694,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -1708,7 +1711,7 @@
         <v>414000</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F18">
         <v>1288027.7959324</v>
@@ -1744,7 +1747,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -1761,7 +1764,7 @@
         <v>414000</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F19">
         <v>1288154.7510168403</v>
@@ -1797,7 +1800,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -1814,7 +1817,7 @@
         <v>414000</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F20">
         <v>1288281.7061012802</v>
@@ -1850,7 +1853,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
@@ -1867,7 +1870,7 @@
         <v>414000</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F21">
         <v>1288408.6611857202</v>
@@ -1903,7 +1906,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -1920,7 +1923,7 @@
         <v>414000</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F22">
         <v>1288535.6162701603</v>
@@ -1956,7 +1959,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -1973,7 +1976,7 @@
         <v>414000</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F23">
         <v>1288662.5713546001</v>
@@ -2009,7 +2012,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -2026,7 +2029,7 @@
         <v>414000</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F24">
         <v>1288789.5264390404</v>
@@ -2062,7 +2065,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
@@ -2079,7 +2082,7 @@
         <v>414000</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F25">
         <v>1288916.4815234803</v>
@@ -2115,7 +2118,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
@@ -2132,7 +2135,7 @@
         <v>414000</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F26">
         <v>1289043.4366079206</v>
@@ -2168,7 +2171,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
@@ -2185,7 +2188,7 @@
         <v>414000</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F27">
         <v>1289170.3916923604</v>
@@ -2221,7 +2224,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -2238,7 +2241,7 @@
         <v>414000</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F28">
         <v>1289297.3467768</v>
@@ -2274,7 +2277,7 @@
         <v>139589.9</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -8865,7 +8868,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71493739-45C2-4A8D-9266-24BB3FC8F4DB}">
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
@@ -8879,7 +8882,7 @@
     <col min="20" max="20" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
@@ -8958,8 +8961,11 @@
       <c r="Z1" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA1" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -9038,8 +9044,11 @@
       <c r="Z2" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
@@ -9118,8 +9127,11 @@
       <c r="Z3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -9198,8 +9210,11 @@
       <c r="Z4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>56</v>
       </c>
@@ -9278,38 +9293,41 @@
       <c r="Z5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED49FD0A-2C9F-4B91-B615-0332AE7669B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDECAE6-5F97-4137-9153-44686F3BABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -860,10 +860,10 @@
         <v>303600</v>
       </c>
       <c r="D2">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F2">
         <v>1775265.6417320003</v>
@@ -872,10 +872,10 @@
         <v>2337972.5216000001</v>
       </c>
       <c r="H2">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J2">
         <v>1052044.8400000001</v>
@@ -884,10 +884,10 @@
         <v>1673707.7</v>
       </c>
       <c r="L2">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N2">
         <v>90210</v>
@@ -896,10 +896,10 @@
         <v>129380</v>
       </c>
       <c r="P2">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q2">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -913,10 +913,10 @@
         <v>299045.40000000002</v>
       </c>
       <c r="D3">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F3">
         <v>1722922.372057667</v>
@@ -925,10 +925,10 @@
         <v>2318026.381866667</v>
       </c>
       <c r="H3">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J3">
         <v>1042480.7960000001</v>
@@ -937,10 +937,10 @@
         <v>1660955.6413333334</v>
       </c>
       <c r="L3">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N3">
         <v>88856.85</v>
@@ -949,10 +949,10 @@
         <v>127438.3</v>
       </c>
       <c r="P3">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q3">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -966,10 +966,10 @@
         <v>294559.71899999998</v>
       </c>
       <c r="D4">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E4">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F4">
         <v>1670579.1023833335</v>
@@ -978,10 +978,10 @@
         <v>2298080.2421333333</v>
       </c>
       <c r="H4">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J4">
         <v>1032916.7520000001</v>
@@ -990,10 +990,10 @@
         <v>1648203.5826666667</v>
       </c>
       <c r="L4">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N4">
         <v>87523</v>
@@ -1002,10 +1002,10 @@
         <v>125526.73</v>
       </c>
       <c r="P4">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q4">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
@@ -1019,10 +1019,10 @@
         <v>290141.32319999998</v>
       </c>
       <c r="D5">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E5">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F5">
         <v>1618235.832709</v>
@@ -1031,10 +1031,10 @@
         <v>2278134.1023999997</v>
       </c>
       <c r="H5">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J5">
         <v>1023352.708</v>
@@ -1043,10 +1043,10 @@
         <v>1635451.524</v>
       </c>
       <c r="L5">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N5">
         <v>86209.15</v>
@@ -1055,10 +1055,10 @@
         <v>123644.83</v>
       </c>
       <c r="P5">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q5">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -1072,10 +1072,10 @@
         <v>285788.2034</v>
       </c>
       <c r="D6">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E6">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F6">
         <v>1565892.5630346665</v>
@@ -1084,10 +1084,10 @@
         <v>2258187.9626666661</v>
       </c>
       <c r="H6">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J6">
         <v>1013788.6639999999</v>
@@ -1096,10 +1096,10 @@
         <v>1622699.4653333335</v>
       </c>
       <c r="L6">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N6">
         <v>84915.01</v>
@@ -1108,10 +1108,10 @@
         <v>121792.16</v>
       </c>
       <c r="P6">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q6">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -1125,10 +1125,10 @@
         <v>281498.4804</v>
       </c>
       <c r="D7">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E7">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F7">
         <v>1513549.293360333</v>
@@ -1137,10 +1137,10 @@
         <v>2238241.8229333302</v>
       </c>
       <c r="H7">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J7">
         <v>1004224.62</v>
@@ -1149,10 +1149,10 @@
         <v>1609947.4066666667</v>
       </c>
       <c r="L7">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N7">
         <v>83640.289999999994</v>
@@ -1161,10 +1161,10 @@
         <v>119968.28</v>
       </c>
       <c r="P7">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q7">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -1178,10 +1178,10 @@
         <v>277270.34419999999</v>
       </c>
       <c r="D8">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E8">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F8">
         <v>1461206.0236859999</v>
@@ -1190,10 +1190,10 @@
         <v>2218295.6831999999</v>
       </c>
       <c r="H8">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J8">
         <v>994660.57600000012</v>
@@ -1202,10 +1202,10 @@
         <v>1597195.3480000002</v>
       </c>
       <c r="L8">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N8">
         <v>82384.69</v>
@@ -1214,10 +1214,10 @@
         <v>118172.75</v>
       </c>
       <c r="P8">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q8">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -1231,10 +1231,10 @@
         <v>273102.28909999999</v>
       </c>
       <c r="D9">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E9">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F9">
         <v>1444015.15599508</v>
@@ -1243,10 +1243,10 @@
         <v>2205259.4561600001</v>
       </c>
       <c r="H9">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J9">
         <v>992747.76720000012</v>
@@ -1255,10 +1255,10 @@
         <v>1594326.1348000003</v>
       </c>
       <c r="L9">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N9">
         <v>81147.92</v>
@@ -1267,10 +1267,10 @@
         <v>116405.16</v>
       </c>
       <c r="P9">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q9">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -1284,10 +1284,10 @@
         <v>268993.2548</v>
       </c>
       <c r="D10">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E10">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F10">
         <v>1426824.2883041599</v>
@@ -1296,10 +1296,10 @@
         <v>2192223.2291199998</v>
       </c>
       <c r="H10">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J10">
         <v>990834.9584</v>
@@ -1308,10 +1308,10 @@
         <v>1591456.9216000002</v>
       </c>
       <c r="L10">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N10">
         <v>79929.7</v>
@@ -1320,10 +1320,10 @@
         <v>114665.09</v>
       </c>
       <c r="P10">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q10">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -1337,10 +1337,10 @@
         <v>264942.41499999998</v>
       </c>
       <c r="D11">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E11">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F11">
         <v>1409633.42061324</v>
@@ -1349,10 +1349,10 @@
         <v>2179187.0020799995</v>
       </c>
       <c r="H11">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J11">
         <v>988922.1496</v>
@@ -1361,10 +1361,10 @@
         <v>1588587.7084000004</v>
       </c>
       <c r="L11">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N11">
         <v>78729.759999999995</v>
@@ -1373,10 +1373,10 @@
         <v>112952.12</v>
       </c>
       <c r="P11">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q11">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -1390,10 +1390,10 @@
         <v>260948.7948</v>
       </c>
       <c r="D12">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E12">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F12">
         <v>1392442.5529223196</v>
@@ -1402,10 +1402,10 @@
         <v>2166150.7750399997</v>
       </c>
       <c r="H12">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J12">
         <v>987009.34079999989</v>
@@ -1414,10 +1414,10 @@
         <v>1585718.4952000002</v>
       </c>
       <c r="L12">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N12">
         <v>77547.820000000007</v>
@@ -1426,10 +1426,10 @@
         <v>111265.84</v>
       </c>
       <c r="P12">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q12">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -1443,10 +1443,10 @@
         <v>257011.4613</v>
       </c>
       <c r="D13">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E13">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F13">
         <v>1375251.6852313997</v>
@@ -1455,10 +1455,10 @@
         <v>2153114.5479999995</v>
       </c>
       <c r="H13">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J13">
         <v>985096.53199999989</v>
@@ -1467,10 +1467,10 @@
         <v>1582849.2820000004</v>
       </c>
       <c r="L13">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N13">
         <v>76383.600000000006</v>
@@ -1479,10 +1479,10 @@
         <v>109605.86</v>
       </c>
       <c r="P13">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q13">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
@@ -1496,10 +1496,10 @@
         <v>253129.39139999999</v>
       </c>
       <c r="D14">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E14">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F14">
         <v>1358060.8175404796</v>
@@ -1508,10 +1508,10 @@
         <v>2140078.3209599997</v>
       </c>
       <c r="H14">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J14">
         <v>983183.72319999977</v>
@@ -1520,10 +1520,10 @@
         <v>1579980.0688000005</v>
       </c>
       <c r="L14">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N14">
         <v>75236.84</v>
@@ -1532,10 +1532,10 @@
         <v>107971.77</v>
       </c>
       <c r="P14">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q14">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -1549,10 +1549,10 @@
         <v>249301.63759999999</v>
       </c>
       <c r="D15">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E15">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F15">
         <v>1340869.9498495597</v>
@@ -1561,10 +1561,10 @@
         <v>2127042.0939199994</v>
       </c>
       <c r="H15">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J15">
         <v>981270.91439999978</v>
@@ -1573,10 +1573,10 @@
         <v>1577110.8556000004</v>
       </c>
       <c r="L15">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N15">
         <v>74107.289999999994</v>
@@ -1585,10 +1585,10 @@
         <v>106363.2</v>
       </c>
       <c r="P15">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q15">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -1602,10 +1602,10 @@
         <v>245527.30809999999</v>
       </c>
       <c r="D16">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E16">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F16">
         <v>1323679.0821586396</v>
@@ -1614,10 +1614,10 @@
         <v>2114005.8668799992</v>
       </c>
       <c r="H16">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J16">
         <v>979358.10559999966</v>
@@ -1626,10 +1626,10 @@
         <v>1574241.6424000005</v>
       </c>
       <c r="L16">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N16">
         <v>72994.679999999993</v>
@@ -1638,10 +1638,10 @@
         <v>104779.75</v>
       </c>
       <c r="P16">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q16">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
@@ -1655,10 +1655,10 @@
         <v>241805.39859999999</v>
       </c>
       <c r="D17">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E17">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F17">
         <v>1306488.2144677194</v>
@@ -1667,10 +1667,10 @@
         <v>2100969.6398399994</v>
       </c>
       <c r="H17">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J17">
         <v>977445.29679999966</v>
@@ -1679,10 +1679,10 @@
         <v>1571372.4292000004</v>
       </c>
       <c r="L17">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N17">
         <v>71898.759999999995</v>
@@ -1691,10 +1691,10 @@
         <v>103221.06</v>
       </c>
       <c r="P17">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q17">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -1708,10 +1708,10 @@
         <v>238134.9901</v>
       </c>
       <c r="D18">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E18">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F18">
         <v>1288027.7959324</v>
@@ -1720,10 +1720,10 @@
         <v>2087933.4128</v>
       </c>
       <c r="H18">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J18">
         <v>975532.48799999955</v>
@@ -1732,10 +1732,10 @@
         <v>1568503.2160000005</v>
       </c>
       <c r="L18">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M18">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N18">
         <v>70819.28</v>
@@ -1744,10 +1744,10 @@
         <v>101686.74</v>
       </c>
       <c r="P18">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q18">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -1761,10 +1761,10 @@
         <v>234515.065</v>
       </c>
       <c r="D19">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E19">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F19">
         <v>1288154.7510168403</v>
@@ -1773,10 +1773,10 @@
         <v>2076927.41784</v>
       </c>
       <c r="H19">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J19">
         <v>973619.67919999966</v>
@@ -1785,10 +1785,10 @@
         <v>1565634.0028000006</v>
       </c>
       <c r="L19">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N19">
         <v>69755.990000000005</v>
@@ -1797,10 +1797,10 @@
         <v>100176.44</v>
       </c>
       <c r="P19">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q19">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -1814,10 +1814,10 @@
         <v>230944.68799999999</v>
       </c>
       <c r="D20">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E20">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F20">
         <v>1288281.7061012802</v>
@@ -1826,10 +1826,10 @@
         <v>2065921.4228800002</v>
       </c>
       <c r="H20">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J20">
         <v>971706.87039999955</v>
@@ -1838,10 +1838,10 @@
         <v>1562764.7896000005</v>
       </c>
       <c r="L20">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N20">
         <v>68708.649999999994</v>
@@ -1850,10 +1850,10 @@
         <v>98689.79</v>
       </c>
       <c r="P20">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q20">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
@@ -1867,10 +1867,10 @@
         <v>227422.96530000001</v>
       </c>
       <c r="D21">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E21">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F21">
         <v>1288408.6611857202</v>
@@ -1879,10 +1879,10 @@
         <v>2054915.4279200002</v>
       </c>
       <c r="H21">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J21">
         <v>969794.06159999955</v>
@@ -1891,10 +1891,10 @@
         <v>1559895.5764000006</v>
       </c>
       <c r="L21">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N21">
         <v>67677.02</v>
@@ -1903,10 +1903,10 @@
         <v>97226.44</v>
       </c>
       <c r="P21">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q21">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -1920,10 +1920,10 @@
         <v>223948.88099999999</v>
       </c>
       <c r="D22">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E22">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F22">
         <v>1288535.6162701603</v>
@@ -1932,10 +1932,10 @@
         <v>2043909.4329600004</v>
       </c>
       <c r="H22">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J22">
         <v>967881.25279999943</v>
@@ -1944,10 +1944,10 @@
         <v>1557026.3632000005</v>
       </c>
       <c r="L22">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N22">
         <v>66660.86</v>
@@ -1956,10 +1956,10 @@
         <v>95786.05</v>
       </c>
       <c r="P22">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q22">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -1973,10 +1973,10 @@
         <v>220521.46350000001</v>
       </c>
       <c r="D23">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E23">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F23">
         <v>1288662.5713546001</v>
@@ -1985,10 +1985,10 @@
         <v>2032903.4380000005</v>
       </c>
       <c r="H23">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J23">
         <v>965968.44399999944</v>
@@ -1997,10 +1997,10 @@
         <v>1554157.1500000006</v>
       </c>
       <c r="L23">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N23">
         <v>65659.95</v>
@@ -2009,10 +2009,10 @@
         <v>94368.26</v>
       </c>
       <c r="P23">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q23">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -2026,10 +2026,10 @@
         <v>217139.74350000001</v>
       </c>
       <c r="D24">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E24">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F24">
         <v>1288789.5264390404</v>
@@ -2038,10 +2038,10 @@
         <v>2021897.4430400007</v>
       </c>
       <c r="H24">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J24">
         <v>964055.63519999932</v>
@@ -2050,10 +2050,10 @@
         <v>1551287.9368000007</v>
       </c>
       <c r="L24">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M24">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N24">
         <v>64674.05</v>
@@ -2062,10 +2062,10 @@
         <v>92972.74</v>
       </c>
       <c r="P24">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q24">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
@@ -2079,10 +2079,10 @@
         <v>213802.75769999999</v>
       </c>
       <c r="D25">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E25">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F25">
         <v>1288916.4815234803</v>
@@ -2091,10 +2091,10 @@
         <v>2010891.4480800009</v>
       </c>
       <c r="H25">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J25">
         <v>962142.82639999932</v>
@@ -2103,10 +2103,10 @@
         <v>1548418.7236000006</v>
       </c>
       <c r="L25">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N25">
         <v>63702.94</v>
@@ -2115,10 +2115,10 @@
         <v>91599.15</v>
       </c>
       <c r="P25">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q25">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
@@ -2132,10 +2132,10 @@
         <v>210509.61679999999</v>
       </c>
       <c r="D26">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E26">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F26">
         <v>1289043.4366079206</v>
@@ -2144,10 +2144,10 @@
         <v>1999885.4531200009</v>
       </c>
       <c r="H26">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J26">
         <v>960230.01759999921</v>
@@ -2156,10 +2156,10 @@
         <v>1545549.5104000007</v>
       </c>
       <c r="L26">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N26">
         <v>62746.400000000001</v>
@@ -2168,10 +2168,10 @@
         <v>90247.16</v>
       </c>
       <c r="P26">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q26">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
@@ -2185,10 +2185,10 @@
         <v>207259.3126</v>
       </c>
       <c r="D27">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E27">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F27">
         <v>1289170.3916923604</v>
@@ -2197,10 +2197,10 @@
         <v>1988879.4581600011</v>
       </c>
       <c r="H27">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J27">
         <v>958317.20879999921</v>
@@ -2209,10 +2209,10 @@
         <v>1542680.2972000006</v>
       </c>
       <c r="L27">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M27">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N27">
         <v>61804.2</v>
@@ -2221,10 +2221,10 @@
         <v>88916.45</v>
       </c>
       <c r="P27">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q27">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -2238,10 +2238,10 @@
         <v>204050.9535</v>
       </c>
       <c r="D28">
-        <v>414000</v>
+        <v>368000</v>
       </c>
       <c r="E28">
-        <v>1000</v>
+        <v>988.8</v>
       </c>
       <c r="F28">
         <v>1289297.3467768</v>
@@ -2250,10 +2250,10 @@
         <v>1977873.4631999999</v>
       </c>
       <c r="H28">
-        <v>2380000</v>
+        <v>496000</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>12537.43</v>
       </c>
       <c r="J28">
         <v>956404.40000000026</v>
@@ -2262,10 +2262,10 @@
         <v>1539811.0840000003</v>
       </c>
       <c r="L28">
-        <v>1700000</v>
+        <v>496000</v>
       </c>
       <c r="M28">
-        <v>1</v>
+        <v>14114.8</v>
       </c>
       <c r="N28">
         <v>60876.14</v>
@@ -2274,10 +2274,10 @@
         <v>87606.7</v>
       </c>
       <c r="P28">
-        <v>139589.9</v>
+        <v>230000</v>
       </c>
       <c r="Q28">
-        <v>1000</v>
+        <v>6512.98</v>
       </c>
     </row>
   </sheetData>
@@ -9012,10 +9012,10 @@
         <v>5</v>
       </c>
       <c r="P2" s="6">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Q2" s="6">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="R2" s="6">
         <v>0.85</v>
@@ -9095,10 +9095,10 @@
         <v>5</v>
       </c>
       <c r="P3" s="6">
-        <v>10000</v>
+        <v>150.27000000000001</v>
       </c>
       <c r="Q3" s="6">
-        <v>10000</v>
+        <v>150.27000000000001</v>
       </c>
       <c r="R3" s="6">
         <v>0.85</v>
@@ -9178,10 +9178,10 @@
         <v>5</v>
       </c>
       <c r="P4" s="6">
-        <v>10000</v>
+        <v>85.3</v>
       </c>
       <c r="Q4" s="6">
-        <v>10000</v>
+        <v>85.3</v>
       </c>
       <c r="R4" s="6">
         <v>0.85</v>
@@ -9243,7 +9243,7 @@
         <v>0.27439999999999998</v>
       </c>
       <c r="J5" s="6">
-        <v>0.27439999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="K5" s="5">
         <v>0.8</v>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDECAE6-5F97-4137-9153-44686F3BABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150F7FBD-CA77-4252-8E4F-5DD69389CF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="114">
   <si>
     <t>Value</t>
   </si>
@@ -223,6 +223,168 @@
   </si>
   <si>
     <t>total_facility_cap_initial</t>
+  </si>
+  <si>
+    <t>280 439,83</t>
+  </si>
+  <si>
+    <t>274 754,91</t>
+  </si>
+  <si>
+    <t>269 179,44</t>
+  </si>
+  <si>
+    <t>263 711,78</t>
+  </si>
+  <si>
+    <t>258 350,32</t>
+  </si>
+  <si>
+    <t>253 093,46</t>
+  </si>
+  <si>
+    <t>247 939,65</t>
+  </si>
+  <si>
+    <t>242 887,37</t>
+  </si>
+  <si>
+    <t>237 935,10</t>
+  </si>
+  <si>
+    <t>233 081,40</t>
+  </si>
+  <si>
+    <t>228 324,82</t>
+  </si>
+  <si>
+    <t>223 663,91</t>
+  </si>
+  <si>
+    <t>219 097,32</t>
+  </si>
+  <si>
+    <t>214 623,65</t>
+  </si>
+  <si>
+    <t>210 241,60</t>
+  </si>
+  <si>
+    <t>205 949,84</t>
+  </si>
+  <si>
+    <t>201 747,12</t>
+  </si>
+  <si>
+    <t>197 632,19</t>
+  </si>
+  <si>
+    <t>193 603,83</t>
+  </si>
+  <si>
+    <t>189 660,87</t>
+  </si>
+  <si>
+    <t>185 802,14</t>
+  </si>
+  <si>
+    <t>182 026,51</t>
+  </si>
+  <si>
+    <t>178 332,87</t>
+  </si>
+  <si>
+    <t>174 720,11</t>
+  </si>
+  <si>
+    <t>171 187,17</t>
+  </si>
+  <si>
+    <t>167 732,98</t>
+  </si>
+  <si>
+    <t>164 356,52</t>
+  </si>
+  <si>
+    <t>527 469,86</t>
+  </si>
+  <si>
+    <t>516 785,56</t>
+  </si>
+  <si>
+    <t>506 302,50</t>
+  </si>
+  <si>
+    <t>496 017,89</t>
+  </si>
+  <si>
+    <t>485 929,01</t>
+  </si>
+  <si>
+    <t>476 033,18</t>
+  </si>
+  <si>
+    <t>466 327,80</t>
+  </si>
+  <si>
+    <t>456 810,30</t>
+  </si>
+  <si>
+    <t>447 478,16</t>
+  </si>
+  <si>
+    <t>438 328,91</t>
+  </si>
+  <si>
+    <t>429 360,14</t>
+  </si>
+  <si>
+    <t>420 569,49</t>
+  </si>
+  <si>
+    <t>411 954,65</t>
+  </si>
+  <si>
+    <t>403 513,36</t>
+  </si>
+  <si>
+    <t>395 243,39</t>
+  </si>
+  <si>
+    <t>387 142,59</t>
+  </si>
+  <si>
+    <t>379 208,83</t>
+  </si>
+  <si>
+    <t>371 440,05</t>
+  </si>
+  <si>
+    <t>363 834,24</t>
+  </si>
+  <si>
+    <t>356 389,41</t>
+  </si>
+  <si>
+    <t>349 103,66</t>
+  </si>
+  <si>
+    <t>341 975,10</t>
+  </si>
+  <si>
+    <t>334 991,90</t>
+  </si>
+  <si>
+    <t>328 152,29</t>
+  </si>
+  <si>
+    <t>321 454,54</t>
+  </si>
+  <si>
+    <t>314 897,00</t>
+  </si>
+  <si>
+    <t>308 477,99</t>
   </si>
 </sst>
 </file>
@@ -791,6 +953,8 @@
     <col min="9" max="9" width="22.5546875" customWidth="1"/>
     <col min="10" max="10" width="24.109375" customWidth="1"/>
     <col min="11" max="11" width="27.6640625" customWidth="1"/>
+    <col min="12" max="12" width="22.88671875" customWidth="1"/>
+    <col min="13" max="13" width="20.109375" customWidth="1"/>
     <col min="15" max="15" width="32.77734375" customWidth="1"/>
     <col min="16" max="16" width="35.21875" customWidth="1"/>
     <col min="17" max="17" width="31.44140625" customWidth="1"/>
@@ -859,47 +1023,47 @@
       <c r="C2">
         <v>303600</v>
       </c>
-      <c r="D2">
-        <v>368000</v>
-      </c>
-      <c r="E2">
-        <v>988.8</v>
-      </c>
-      <c r="F2">
+      <c r="D2" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E2" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F2" s="8">
         <v>1775265.6417320003</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="8">
         <v>2337972.5216000001</v>
       </c>
-      <c r="H2">
-        <v>496000</v>
-      </c>
-      <c r="I2">
-        <v>12537.43</v>
-      </c>
-      <c r="J2">
+      <c r="H2" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I2" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J2" s="8">
         <v>1052044.8400000001</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="8">
         <v>1673707.7</v>
       </c>
-      <c r="L2">
-        <v>496000</v>
+      <c r="L2" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M2">
-        <v>14114.8</v>
-      </c>
-      <c r="N2">
-        <v>90210</v>
-      </c>
-      <c r="O2" s="8">
-        <v>129380</v>
-      </c>
-      <c r="P2">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q2">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -912,47 +1076,47 @@
       <c r="C3">
         <v>299045.40000000002</v>
       </c>
-      <c r="D3">
-        <v>368000</v>
-      </c>
-      <c r="E3">
-        <v>988.8</v>
-      </c>
-      <c r="F3">
+      <c r="D3" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E3" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F3" s="8">
         <v>1722922.372057667</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="8">
         <v>2318026.381866667</v>
       </c>
-      <c r="H3">
-        <v>496000</v>
-      </c>
-      <c r="I3">
-        <v>12537.43</v>
-      </c>
-      <c r="J3">
+      <c r="H3" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I3" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J3" s="8">
         <v>1042480.7960000001</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="8">
         <v>1660955.6413333334</v>
       </c>
-      <c r="L3">
-        <v>496000</v>
+      <c r="L3" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M3">
-        <v>14114.8</v>
-      </c>
-      <c r="N3">
-        <v>88856.85</v>
-      </c>
-      <c r="O3" s="8">
-        <v>127438.3</v>
-      </c>
-      <c r="P3">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P3" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q3">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -965,47 +1129,47 @@
       <c r="C4">
         <v>294559.71899999998</v>
       </c>
-      <c r="D4">
-        <v>368000</v>
-      </c>
-      <c r="E4">
-        <v>988.8</v>
-      </c>
-      <c r="F4">
+      <c r="D4" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F4" s="8">
         <v>1670579.1023833335</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="8">
         <v>2298080.2421333333</v>
       </c>
-      <c r="H4">
-        <v>496000</v>
-      </c>
-      <c r="I4">
-        <v>12537.43</v>
-      </c>
-      <c r="J4">
+      <c r="H4" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I4" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J4" s="8">
         <v>1032916.7520000001</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="8">
         <v>1648203.5826666667</v>
       </c>
-      <c r="L4">
-        <v>496000</v>
+      <c r="L4" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M4">
-        <v>14114.8</v>
-      </c>
-      <c r="N4">
-        <v>87523</v>
-      </c>
-      <c r="O4" s="8">
-        <v>125526.73</v>
-      </c>
-      <c r="P4">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="P4" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q4">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
@@ -1018,47 +1182,47 @@
       <c r="C5">
         <v>290141.32319999998</v>
       </c>
-      <c r="D5">
-        <v>368000</v>
-      </c>
-      <c r="E5">
-        <v>988.8</v>
-      </c>
-      <c r="F5">
+      <c r="D5" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="8">
         <v>1618235.832709</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="8">
         <v>2278134.1023999997</v>
       </c>
-      <c r="H5">
-        <v>496000</v>
-      </c>
-      <c r="I5">
-        <v>12537.43</v>
-      </c>
-      <c r="J5">
+      <c r="H5" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I5" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J5" s="8">
         <v>1023352.708</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="8">
         <v>1635451.524</v>
       </c>
-      <c r="L5">
-        <v>496000</v>
+      <c r="L5" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M5">
-        <v>14114.8</v>
-      </c>
-      <c r="N5">
-        <v>86209.15</v>
-      </c>
-      <c r="O5" s="8">
-        <v>123644.83</v>
-      </c>
-      <c r="P5">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="P5" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q5">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -1071,47 +1235,47 @@
       <c r="C6">
         <v>285788.2034</v>
       </c>
-      <c r="D6">
-        <v>368000</v>
-      </c>
-      <c r="E6">
-        <v>988.8</v>
-      </c>
-      <c r="F6">
+      <c r="D6" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="8">
         <v>1565892.5630346665</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="8">
         <v>2258187.9626666661</v>
       </c>
-      <c r="H6">
-        <v>496000</v>
-      </c>
-      <c r="I6">
-        <v>12537.43</v>
-      </c>
-      <c r="J6">
+      <c r="H6" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I6" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J6" s="8">
         <v>1013788.6639999999</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="8">
         <v>1622699.4653333335</v>
       </c>
-      <c r="L6">
-        <v>496000</v>
+      <c r="L6" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M6">
-        <v>14114.8</v>
-      </c>
-      <c r="N6">
-        <v>84915.01</v>
-      </c>
-      <c r="O6" s="8">
-        <v>121792.16</v>
-      </c>
-      <c r="P6">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P6" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q6">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -1124,47 +1288,47 @@
       <c r="C7">
         <v>281498.4804</v>
       </c>
-      <c r="D7">
-        <v>368000</v>
-      </c>
-      <c r="E7">
-        <v>988.8</v>
-      </c>
-      <c r="F7">
+      <c r="D7" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F7" s="8">
         <v>1513549.293360333</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="8">
         <v>2238241.8229333302</v>
       </c>
-      <c r="H7">
-        <v>496000</v>
-      </c>
-      <c r="I7">
-        <v>12537.43</v>
-      </c>
-      <c r="J7">
+      <c r="H7" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J7" s="8">
         <v>1004224.62</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="8">
         <v>1609947.4066666667</v>
       </c>
-      <c r="L7">
-        <v>496000</v>
+      <c r="L7" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M7">
-        <v>14114.8</v>
-      </c>
-      <c r="N7">
-        <v>83640.289999999994</v>
-      </c>
-      <c r="O7" s="8">
-        <v>119968.28</v>
-      </c>
-      <c r="P7">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P7" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q7">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -1177,47 +1341,47 @@
       <c r="C8">
         <v>277270.34419999999</v>
       </c>
-      <c r="D8">
-        <v>368000</v>
-      </c>
-      <c r="E8">
-        <v>988.8</v>
-      </c>
-      <c r="F8">
+      <c r="D8" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F8" s="8">
         <v>1461206.0236859999</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="8">
         <v>2218295.6831999999</v>
       </c>
-      <c r="H8">
-        <v>496000</v>
-      </c>
-      <c r="I8">
-        <v>12537.43</v>
-      </c>
-      <c r="J8">
+      <c r="H8" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="8">
         <v>994660.57600000012</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="8">
         <v>1597195.3480000002</v>
       </c>
-      <c r="L8">
-        <v>496000</v>
+      <c r="L8" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M8">
-        <v>14114.8</v>
-      </c>
-      <c r="N8">
-        <v>82384.69</v>
-      </c>
-      <c r="O8" s="8">
-        <v>118172.75</v>
-      </c>
-      <c r="P8">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P8" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q8">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -1230,47 +1394,47 @@
       <c r="C9">
         <v>273102.28909999999</v>
       </c>
-      <c r="D9">
-        <v>368000</v>
-      </c>
-      <c r="E9">
-        <v>988.8</v>
-      </c>
-      <c r="F9">
+      <c r="D9" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="8">
         <v>1444015.15599508</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="8">
         <v>2205259.4561600001</v>
       </c>
-      <c r="H9">
-        <v>496000</v>
-      </c>
-      <c r="I9">
-        <v>12537.43</v>
-      </c>
-      <c r="J9">
+      <c r="H9" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J9" s="8">
         <v>992747.76720000012</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="8">
         <v>1594326.1348000003</v>
       </c>
-      <c r="L9">
-        <v>496000</v>
+      <c r="L9" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M9">
-        <v>14114.8</v>
-      </c>
-      <c r="N9">
-        <v>81147.92</v>
-      </c>
-      <c r="O9" s="8">
-        <v>116405.16</v>
-      </c>
-      <c r="P9">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="P9" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q9">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -1283,47 +1447,47 @@
       <c r="C10">
         <v>268993.2548</v>
       </c>
-      <c r="D10">
-        <v>368000</v>
-      </c>
-      <c r="E10">
-        <v>988.8</v>
-      </c>
-      <c r="F10">
+      <c r="D10" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="8">
         <v>1426824.2883041599</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="8">
         <v>2192223.2291199998</v>
       </c>
-      <c r="H10">
-        <v>496000</v>
-      </c>
-      <c r="I10">
-        <v>12537.43</v>
-      </c>
-      <c r="J10">
+      <c r="H10" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I10" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="8">
         <v>990834.9584</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="8">
         <v>1591456.9216000002</v>
       </c>
-      <c r="L10">
-        <v>496000</v>
+      <c r="L10" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M10">
-        <v>14114.8</v>
-      </c>
-      <c r="N10">
-        <v>79929.7</v>
-      </c>
-      <c r="O10" s="8">
-        <v>114665.09</v>
-      </c>
-      <c r="P10">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="P10" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q10">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -1336,47 +1500,47 @@
       <c r="C11">
         <v>264942.41499999998</v>
       </c>
-      <c r="D11">
-        <v>368000</v>
-      </c>
-      <c r="E11">
-        <v>988.8</v>
-      </c>
-      <c r="F11">
+      <c r="D11" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="8">
         <v>1409633.42061324</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="8">
         <v>2179187.0020799995</v>
       </c>
-      <c r="H11">
-        <v>496000</v>
-      </c>
-      <c r="I11">
-        <v>12537.43</v>
-      </c>
-      <c r="J11">
+      <c r="H11" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J11" s="8">
         <v>988922.1496</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="8">
         <v>1588587.7084000004</v>
       </c>
-      <c r="L11">
-        <v>496000</v>
+      <c r="L11" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M11">
-        <v>14114.8</v>
-      </c>
-      <c r="N11">
-        <v>78729.759999999995</v>
-      </c>
-      <c r="O11" s="8">
-        <v>112952.12</v>
-      </c>
-      <c r="P11">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="P11" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q11">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -1389,47 +1553,47 @@
       <c r="C12">
         <v>260948.7948</v>
       </c>
-      <c r="D12">
-        <v>368000</v>
-      </c>
-      <c r="E12">
-        <v>988.8</v>
-      </c>
-      <c r="F12">
+      <c r="D12" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="8">
         <v>1392442.5529223196</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="8">
         <v>2166150.7750399997</v>
       </c>
-      <c r="H12">
-        <v>496000</v>
-      </c>
-      <c r="I12">
-        <v>12537.43</v>
-      </c>
-      <c r="J12">
+      <c r="H12" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I12" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J12" s="8">
         <v>987009.34079999989</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="8">
         <v>1585718.4952000002</v>
       </c>
-      <c r="L12">
-        <v>496000</v>
+      <c r="L12" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M12">
-        <v>14114.8</v>
-      </c>
-      <c r="N12">
-        <v>77547.820000000007</v>
-      </c>
-      <c r="O12" s="8">
-        <v>111265.84</v>
-      </c>
-      <c r="P12">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P12" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q12">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -1442,47 +1606,47 @@
       <c r="C13">
         <v>257011.4613</v>
       </c>
-      <c r="D13">
-        <v>368000</v>
-      </c>
-      <c r="E13">
-        <v>988.8</v>
-      </c>
-      <c r="F13">
+      <c r="D13" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="8">
         <v>1375251.6852313997</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="8">
         <v>2153114.5479999995</v>
       </c>
-      <c r="H13">
-        <v>496000</v>
-      </c>
-      <c r="I13">
-        <v>12537.43</v>
-      </c>
-      <c r="J13">
+      <c r="H13" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J13" s="8">
         <v>985096.53199999989</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="8">
         <v>1582849.2820000004</v>
       </c>
-      <c r="L13">
-        <v>496000</v>
+      <c r="L13" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M13">
-        <v>14114.8</v>
-      </c>
-      <c r="N13">
-        <v>76383.600000000006</v>
-      </c>
-      <c r="O13" s="8">
-        <v>109605.86</v>
-      </c>
-      <c r="P13">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P13" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q13">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
@@ -1495,47 +1659,47 @@
       <c r="C14">
         <v>253129.39139999999</v>
       </c>
-      <c r="D14">
-        <v>368000</v>
-      </c>
-      <c r="E14">
-        <v>988.8</v>
-      </c>
-      <c r="F14">
+      <c r="D14" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="8">
         <v>1358060.8175404796</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="8">
         <v>2140078.3209599997</v>
       </c>
-      <c r="H14">
-        <v>496000</v>
-      </c>
-      <c r="I14">
-        <v>12537.43</v>
-      </c>
-      <c r="J14">
+      <c r="H14" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I14" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J14" s="8">
         <v>983183.72319999977</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="8">
         <v>1579980.0688000005</v>
       </c>
-      <c r="L14">
-        <v>496000</v>
+      <c r="L14" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M14">
-        <v>14114.8</v>
-      </c>
-      <c r="N14">
-        <v>75236.84</v>
-      </c>
-      <c r="O14" s="8">
-        <v>107971.77</v>
-      </c>
-      <c r="P14">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="P14" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q14">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -1548,47 +1712,47 @@
       <c r="C15">
         <v>249301.63759999999</v>
       </c>
-      <c r="D15">
-        <v>368000</v>
-      </c>
-      <c r="E15">
-        <v>988.8</v>
-      </c>
-      <c r="F15">
+      <c r="D15" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="8">
         <v>1340869.9498495597</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="8">
         <v>2127042.0939199994</v>
       </c>
-      <c r="H15">
-        <v>496000</v>
-      </c>
-      <c r="I15">
-        <v>12537.43</v>
-      </c>
-      <c r="J15">
+      <c r="H15" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I15" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J15" s="8">
         <v>981270.91439999978</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="8">
         <v>1577110.8556000004</v>
       </c>
-      <c r="L15">
-        <v>496000</v>
+      <c r="L15" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M15">
-        <v>14114.8</v>
-      </c>
-      <c r="N15">
-        <v>74107.289999999994</v>
-      </c>
-      <c r="O15">
-        <v>106363.2</v>
-      </c>
-      <c r="P15">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P15" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q15">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -1601,47 +1765,47 @@
       <c r="C16">
         <v>245527.30809999999</v>
       </c>
-      <c r="D16">
-        <v>368000</v>
-      </c>
-      <c r="E16">
-        <v>988.8</v>
-      </c>
-      <c r="F16">
+      <c r="D16" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F16" s="8">
         <v>1323679.0821586396</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="8">
         <v>2114005.8668799992</v>
       </c>
-      <c r="H16">
-        <v>496000</v>
-      </c>
-      <c r="I16">
-        <v>12537.43</v>
-      </c>
-      <c r="J16">
+      <c r="H16" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J16" s="8">
         <v>979358.10559999966</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="8">
         <v>1574241.6424000005</v>
       </c>
-      <c r="L16">
-        <v>496000</v>
+      <c r="L16" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M16">
-        <v>14114.8</v>
-      </c>
-      <c r="N16">
-        <v>72994.679999999993</v>
-      </c>
-      <c r="O16">
-        <v>104779.75</v>
-      </c>
-      <c r="P16">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P16" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q16">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
@@ -1654,47 +1818,47 @@
       <c r="C17">
         <v>241805.39859999999</v>
       </c>
-      <c r="D17">
-        <v>368000</v>
-      </c>
-      <c r="E17">
-        <v>988.8</v>
-      </c>
-      <c r="F17">
+      <c r="D17" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F17" s="8">
         <v>1306488.2144677194</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="8">
         <v>2100969.6398399994</v>
       </c>
-      <c r="H17">
-        <v>496000</v>
-      </c>
-      <c r="I17">
-        <v>12537.43</v>
-      </c>
-      <c r="J17">
+      <c r="H17" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I17" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J17" s="8">
         <v>977445.29679999966</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="8">
         <v>1571372.4292000004</v>
       </c>
-      <c r="L17">
-        <v>496000</v>
+      <c r="L17" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M17">
-        <v>14114.8</v>
-      </c>
-      <c r="N17">
-        <v>71898.759999999995</v>
-      </c>
-      <c r="O17">
-        <v>103221.06</v>
-      </c>
-      <c r="P17">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P17" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q17">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -1707,47 +1871,47 @@
       <c r="C18">
         <v>238134.9901</v>
       </c>
-      <c r="D18">
-        <v>368000</v>
-      </c>
-      <c r="E18">
-        <v>988.8</v>
-      </c>
-      <c r="F18">
+      <c r="D18" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F18" s="8">
         <v>1288027.7959324</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="8">
         <v>2087933.4128</v>
       </c>
-      <c r="H18">
-        <v>496000</v>
-      </c>
-      <c r="I18">
-        <v>12537.43</v>
-      </c>
-      <c r="J18">
+      <c r="H18" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I18" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J18" s="8">
         <v>975532.48799999955</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="8">
         <v>1568503.2160000005</v>
       </c>
-      <c r="L18">
-        <v>496000</v>
+      <c r="L18" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M18">
-        <v>14114.8</v>
-      </c>
-      <c r="N18">
-        <v>70819.28</v>
-      </c>
-      <c r="O18">
-        <v>101686.74</v>
-      </c>
-      <c r="P18">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P18" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q18">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -1760,47 +1924,47 @@
       <c r="C19">
         <v>234515.065</v>
       </c>
-      <c r="D19">
-        <v>368000</v>
-      </c>
-      <c r="E19">
-        <v>988.8</v>
-      </c>
-      <c r="F19">
+      <c r="D19" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F19" s="8">
         <v>1288154.7510168403</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="8">
         <v>2076927.41784</v>
       </c>
-      <c r="H19">
-        <v>496000</v>
-      </c>
-      <c r="I19">
-        <v>12537.43</v>
-      </c>
-      <c r="J19">
+      <c r="H19" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I19" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J19" s="8">
         <v>973619.67919999966</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="8">
         <v>1565634.0028000006</v>
       </c>
-      <c r="L19">
-        <v>496000</v>
+      <c r="L19" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M19">
-        <v>14114.8</v>
-      </c>
-      <c r="N19">
-        <v>69755.990000000005</v>
-      </c>
-      <c r="O19">
-        <v>100176.44</v>
-      </c>
-      <c r="P19">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P19" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q19">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -1813,47 +1977,47 @@
       <c r="C20">
         <v>230944.68799999999</v>
       </c>
-      <c r="D20">
-        <v>368000</v>
-      </c>
-      <c r="E20">
-        <v>988.8</v>
-      </c>
-      <c r="F20">
+      <c r="D20" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="8">
         <v>1288281.7061012802</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="8">
         <v>2065921.4228800002</v>
       </c>
-      <c r="H20">
-        <v>496000</v>
-      </c>
-      <c r="I20">
-        <v>12537.43</v>
-      </c>
-      <c r="J20">
+      <c r="H20" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I20" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J20" s="8">
         <v>971706.87039999955</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="8">
         <v>1562764.7896000005</v>
       </c>
-      <c r="L20">
-        <v>496000</v>
+      <c r="L20" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M20">
-        <v>14114.8</v>
-      </c>
-      <c r="N20">
-        <v>68708.649999999994</v>
-      </c>
-      <c r="O20">
-        <v>98689.79</v>
-      </c>
-      <c r="P20">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="P20" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q20">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
@@ -1866,47 +2030,47 @@
       <c r="C21">
         <v>227422.96530000001</v>
       </c>
-      <c r="D21">
-        <v>368000</v>
-      </c>
-      <c r="E21">
-        <v>988.8</v>
-      </c>
-      <c r="F21">
+      <c r="D21" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F21" s="8">
         <v>1288408.6611857202</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="8">
         <v>2054915.4279200002</v>
       </c>
-      <c r="H21">
-        <v>496000</v>
-      </c>
-      <c r="I21">
-        <v>12537.43</v>
-      </c>
-      <c r="J21">
+      <c r="H21" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I21" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J21" s="8">
         <v>969794.06159999955</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="8">
         <v>1559895.5764000006</v>
       </c>
-      <c r="L21">
-        <v>496000</v>
+      <c r="L21" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M21">
-        <v>14114.8</v>
-      </c>
-      <c r="N21">
-        <v>67677.02</v>
-      </c>
-      <c r="O21">
-        <v>97226.44</v>
-      </c>
-      <c r="P21">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="P21" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q21">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -1919,47 +2083,47 @@
       <c r="C22">
         <v>223948.88099999999</v>
       </c>
-      <c r="D22">
-        <v>368000</v>
-      </c>
-      <c r="E22">
-        <v>988.8</v>
-      </c>
-      <c r="F22">
+      <c r="D22" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F22" s="8">
         <v>1288535.6162701603</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="8">
         <v>2043909.4329600004</v>
       </c>
-      <c r="H22">
-        <v>496000</v>
-      </c>
-      <c r="I22">
-        <v>12537.43</v>
-      </c>
-      <c r="J22">
+      <c r="H22" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I22" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J22" s="8">
         <v>967881.25279999943</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="8">
         <v>1557026.3632000005</v>
       </c>
-      <c r="L22">
-        <v>496000</v>
+      <c r="L22" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M22">
-        <v>14114.8</v>
-      </c>
-      <c r="N22">
-        <v>66660.86</v>
-      </c>
-      <c r="O22">
-        <v>95786.05</v>
-      </c>
-      <c r="P22">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P22" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q22">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -1972,47 +2136,47 @@
       <c r="C23">
         <v>220521.46350000001</v>
       </c>
-      <c r="D23">
-        <v>368000</v>
-      </c>
-      <c r="E23">
-        <v>988.8</v>
-      </c>
-      <c r="F23">
+      <c r="D23" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F23" s="8">
         <v>1288662.5713546001</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="8">
         <v>2032903.4380000005</v>
       </c>
-      <c r="H23">
-        <v>496000</v>
-      </c>
-      <c r="I23">
-        <v>12537.43</v>
-      </c>
-      <c r="J23">
+      <c r="H23" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I23" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J23" s="8">
         <v>965968.44399999944</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="8">
         <v>1554157.1500000006</v>
       </c>
-      <c r="L23">
-        <v>496000</v>
+      <c r="L23" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M23">
-        <v>14114.8</v>
-      </c>
-      <c r="N23">
-        <v>65659.95</v>
-      </c>
-      <c r="O23">
-        <v>94368.26</v>
-      </c>
-      <c r="P23">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P23" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q23">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -2025,47 +2189,47 @@
       <c r="C24">
         <v>217139.74350000001</v>
       </c>
-      <c r="D24">
-        <v>368000</v>
-      </c>
-      <c r="E24">
-        <v>988.8</v>
-      </c>
-      <c r="F24">
+      <c r="D24" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F24" s="8">
         <v>1288789.5264390404</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="8">
         <v>2021897.4430400007</v>
       </c>
-      <c r="H24">
-        <v>496000</v>
-      </c>
-      <c r="I24">
-        <v>12537.43</v>
-      </c>
-      <c r="J24">
+      <c r="H24" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I24" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J24" s="8">
         <v>964055.63519999932</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="8">
         <v>1551287.9368000007</v>
       </c>
-      <c r="L24">
-        <v>496000</v>
+      <c r="L24" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M24">
-        <v>14114.8</v>
-      </c>
-      <c r="N24">
-        <v>64674.05</v>
-      </c>
-      <c r="O24">
-        <v>92972.74</v>
-      </c>
-      <c r="P24">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="P24" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q24">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
@@ -2078,47 +2242,47 @@
       <c r="C25">
         <v>213802.75769999999</v>
       </c>
-      <c r="D25">
-        <v>368000</v>
-      </c>
-      <c r="E25">
-        <v>988.8</v>
-      </c>
-      <c r="F25">
+      <c r="D25" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F25" s="8">
         <v>1288916.4815234803</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="8">
         <v>2010891.4480800009</v>
       </c>
-      <c r="H25">
-        <v>496000</v>
-      </c>
-      <c r="I25">
-        <v>12537.43</v>
-      </c>
-      <c r="J25">
+      <c r="H25" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I25" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J25" s="8">
         <v>962142.82639999932</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="8">
         <v>1548418.7236000006</v>
       </c>
-      <c r="L25">
-        <v>496000</v>
+      <c r="L25" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M25">
-        <v>14114.8</v>
-      </c>
-      <c r="N25">
-        <v>63702.94</v>
-      </c>
-      <c r="O25">
-        <v>91599.15</v>
-      </c>
-      <c r="P25">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="P25" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q25">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
@@ -2131,47 +2295,47 @@
       <c r="C26">
         <v>210509.61679999999</v>
       </c>
-      <c r="D26">
-        <v>368000</v>
-      </c>
-      <c r="E26">
-        <v>988.8</v>
-      </c>
-      <c r="F26">
+      <c r="D26" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="8">
         <v>1289043.4366079206</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="8">
         <v>1999885.4531200009</v>
       </c>
-      <c r="H26">
-        <v>496000</v>
-      </c>
-      <c r="I26">
-        <v>12537.43</v>
-      </c>
-      <c r="J26">
+      <c r="H26" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I26" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J26" s="8">
         <v>960230.01759999921</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="8">
         <v>1545549.5104000007</v>
       </c>
-      <c r="L26">
-        <v>496000</v>
+      <c r="L26" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M26">
-        <v>14114.8</v>
-      </c>
-      <c r="N26">
-        <v>62746.400000000001</v>
-      </c>
-      <c r="O26">
-        <v>90247.16</v>
-      </c>
-      <c r="P26">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P26" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q26">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
@@ -2184,47 +2348,47 @@
       <c r="C27">
         <v>207259.3126</v>
       </c>
-      <c r="D27">
-        <v>368000</v>
-      </c>
-      <c r="E27">
-        <v>988.8</v>
-      </c>
-      <c r="F27">
+      <c r="D27" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="8">
         <v>1289170.3916923604</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="8">
         <v>1988879.4581600011</v>
       </c>
-      <c r="H27">
-        <v>496000</v>
-      </c>
-      <c r="I27">
-        <v>12537.43</v>
-      </c>
-      <c r="J27">
+      <c r="H27" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I27" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J27" s="8">
         <v>958317.20879999921</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="8">
         <v>1542680.2972000006</v>
       </c>
-      <c r="L27">
-        <v>496000</v>
+      <c r="L27" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M27">
-        <v>14114.8</v>
-      </c>
-      <c r="N27">
-        <v>61804.2</v>
-      </c>
-      <c r="O27">
-        <v>88916.45</v>
-      </c>
-      <c r="P27">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P27" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q27">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -2237,47 +2401,47 @@
       <c r="C28">
         <v>204050.9535</v>
       </c>
-      <c r="D28">
-        <v>368000</v>
-      </c>
-      <c r="E28">
-        <v>988.8</v>
-      </c>
-      <c r="F28">
+      <c r="D28" s="8">
+        <v>227700</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F28" s="8">
         <v>1289297.3467768</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="8">
         <v>1977873.4631999999</v>
       </c>
-      <c r="H28">
-        <v>496000</v>
-      </c>
-      <c r="I28">
-        <v>12537.43</v>
-      </c>
-      <c r="J28">
+      <c r="H28" s="8">
+        <v>1646946.1610000001</v>
+      </c>
+      <c r="I28" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J28" s="8">
         <v>956404.40000000026</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="8">
         <v>1539811.0840000003</v>
       </c>
-      <c r="L28">
-        <v>496000</v>
+      <c r="L28" s="8">
+        <v>1093231.041</v>
       </c>
       <c r="M28">
-        <v>14114.8</v>
-      </c>
-      <c r="N28">
-        <v>60876.14</v>
-      </c>
-      <c r="O28">
-        <v>87606.7</v>
-      </c>
-      <c r="P28">
-        <v>230000</v>
+        <v>1000</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P28" s="8">
+        <v>489061.86</v>
       </c>
       <c r="Q28">
-        <v>6512.98</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -8985,7 +9149,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="6">
-        <v>1500</v>
+        <v>13000</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -9012,10 +9176,10 @@
         <v>5</v>
       </c>
       <c r="P2" s="6">
-        <v>90</v>
+        <v>76.923000000000002</v>
       </c>
       <c r="Q2" s="6">
-        <v>90</v>
+        <v>76.923000000000002</v>
       </c>
       <c r="R2" s="6">
         <v>0.85</v>
@@ -9095,13 +9259,13 @@
         <v>5</v>
       </c>
       <c r="P3" s="6">
-        <v>150.27000000000001</v>
+        <v>126.83</v>
       </c>
       <c r="Q3" s="6">
-        <v>150.27000000000001</v>
+        <v>126.83</v>
       </c>
       <c r="R3" s="6">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S3" s="6">
         <v>0.2</v>
@@ -9178,13 +9342,13 @@
         <v>5</v>
       </c>
       <c r="P4" s="6">
-        <v>85.3</v>
+        <v>126.83</v>
       </c>
       <c r="Q4" s="6">
-        <v>85.3</v>
+        <v>126.83</v>
       </c>
       <c r="R4" s="6">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S4" s="6">
         <v>0.2</v>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA2D59B-8BB7-4815-BB60-5AF9193FB5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7503729A-C057-4E46-ADEE-6887F65A1064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -544,7 +544,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -562,6 +562,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
@@ -10512,13 +10513,13 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>70000</v>
-      </c>
-      <c r="C2">
-        <v>26250</v>
-      </c>
-      <c r="D2">
-        <v>36915</v>
+        <v>65.5</v>
+      </c>
+      <c r="C2" s="9">
+        <v>2.1</v>
+      </c>
+      <c r="D2" s="9">
+        <v>15.28</v>
       </c>
       <c r="E2">
         <v>999999</v>
@@ -10529,13 +10530,14 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>70000</v>
-      </c>
-      <c r="C3">
-        <v>26250</v>
-      </c>
-      <c r="D3">
-        <v>36915</v>
+        <f>SUM(B2*1.04)</f>
+        <v>68.12</v>
+      </c>
+      <c r="C3" s="9">
+        <v>2.1</v>
+      </c>
+      <c r="D3" s="9">
+        <v>15.28</v>
       </c>
       <c r="E3">
         <v>999999</v>
@@ -10546,13 +10548,14 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>70000</v>
-      </c>
-      <c r="C4">
-        <v>26250</v>
-      </c>
-      <c r="D4">
-        <v>36915</v>
+        <f t="shared" ref="B4:B9" si="0">SUM(B3*1.04)</f>
+        <v>70.844800000000006</v>
+      </c>
+      <c r="C4" s="9">
+        <v>3.96</v>
+      </c>
+      <c r="D4" s="9">
+        <v>15.85</v>
       </c>
       <c r="E4">
         <v>999999</v>
@@ -10563,13 +10566,14 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>70000</v>
-      </c>
-      <c r="C5">
-        <v>26250</v>
-      </c>
-      <c r="D5">
-        <v>36915</v>
+        <f t="shared" si="0"/>
+        <v>73.678592000000009</v>
+      </c>
+      <c r="C5" s="9">
+        <v>3.42</v>
+      </c>
+      <c r="D5" s="9">
+        <v>18.7</v>
       </c>
       <c r="E5">
         <v>999999</v>
@@ -10580,13 +10584,14 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>70000</v>
-      </c>
-      <c r="C6">
-        <v>26250</v>
-      </c>
-      <c r="D6">
-        <v>36915</v>
+        <f t="shared" si="0"/>
+        <v>76.625735680000005</v>
+      </c>
+      <c r="C6" s="9">
+        <v>4.99</v>
+      </c>
+      <c r="D6" s="9">
+        <v>20.440000000000001</v>
       </c>
       <c r="E6">
         <v>999999</v>
@@ -10597,13 +10602,14 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>70000</v>
-      </c>
-      <c r="C7">
-        <v>26250</v>
-      </c>
-      <c r="D7">
-        <v>36915</v>
+        <f t="shared" si="0"/>
+        <v>79.690765107200008</v>
+      </c>
+      <c r="C7" s="9">
+        <v>6.41</v>
+      </c>
+      <c r="D7" s="9">
+        <v>20.9</v>
       </c>
       <c r="E7">
         <v>999999</v>
@@ -10614,13 +10620,14 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>70000</v>
-      </c>
-      <c r="C8">
-        <v>26250</v>
-      </c>
-      <c r="D8">
-        <v>21800</v>
+        <f t="shared" si="0"/>
+        <v>82.878395711488011</v>
+      </c>
+      <c r="C8" s="9">
+        <v>6.31</v>
+      </c>
+      <c r="D8" s="9">
+        <v>21.8</v>
       </c>
       <c r="E8">
         <v>999999</v>
@@ -10631,13 +10638,15 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>70000</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C9">
-        <v>26250</v>
+        <f>SUM(C8*1.2465)</f>
+        <v>7.8654149999999987</v>
       </c>
       <c r="D9">
-        <v>21800</v>
+        <f>SUM(D8*1.0626)</f>
+        <v>23.164680000000001</v>
       </c>
       <c r="E9">
         <v>999999</v>
@@ -10648,13 +10657,15 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>70000</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C10">
-        <v>26250</v>
+        <f t="shared" ref="C10:C12" si="1">SUM(C9*1.2465)</f>
+        <v>9.8042397974999975</v>
       </c>
       <c r="D10">
-        <v>21800</v>
+        <f t="shared" ref="D10:D13" si="2">SUM(D9*1.0626)</f>
+        <v>24.614788967999999</v>
       </c>
       <c r="E10">
         <v>999999</v>
@@ -10665,13 +10676,15 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>70000</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C11">
-        <v>26250</v>
+        <f t="shared" si="1"/>
+        <v>12.220984907583746</v>
       </c>
       <c r="D11">
-        <v>21800</v>
+        <f t="shared" si="2"/>
+        <v>26.155674757396799</v>
       </c>
       <c r="E11">
         <v>999999</v>
@@ -10682,13 +10695,15 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>70000</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C12">
-        <v>26250</v>
+        <f t="shared" si="1"/>
+        <v>15.233457687303138</v>
       </c>
       <c r="D12">
-        <v>21800</v>
+        <f t="shared" si="2"/>
+        <v>27.793019997209839</v>
       </c>
       <c r="E12">
         <v>999999</v>
@@ -10699,13 +10714,15 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>70000</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C13">
-        <v>26250</v>
+        <f>SUM(C12*1.2465)</f>
+        <v>18.98850500722336</v>
       </c>
       <c r="D13">
-        <v>21800</v>
+        <f t="shared" si="2"/>
+        <v>29.532863049035175</v>
       </c>
       <c r="E13">
         <v>999999</v>
@@ -10716,13 +10733,13 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>70000</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C14">
-        <v>26250</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D14">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E14">
         <v>999999</v>
@@ -10733,13 +10750,13 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>70000</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C15">
-        <v>26250</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D15">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E15">
         <v>999999</v>
@@ -10750,13 +10767,13 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>70000</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C16">
-        <v>26250</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D16">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E16">
         <v>999999</v>
@@ -10767,13 +10784,13 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>70000</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C17">
-        <v>26250</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D17">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E17">
         <v>999999</v>
@@ -10784,13 +10801,13 @@
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C18">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D18">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E18">
         <v>999999</v>
@@ -10801,13 +10818,13 @@
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C19">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D19">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E19">
         <v>999999</v>
@@ -10818,13 +10835,13 @@
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C20">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D20">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E20">
         <v>999999</v>
@@ -10835,13 +10852,13 @@
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C21">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D21">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E21">
         <v>999999</v>
@@ -10852,13 +10869,13 @@
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C22">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D22">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E22">
         <v>999999</v>
@@ -10869,13 +10886,13 @@
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C23">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D23">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E23">
         <v>999999</v>
@@ -10886,13 +10903,13 @@
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C24">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D24">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E24">
         <v>999999</v>
@@ -10903,13 +10920,13 @@
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C25">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D25">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E25">
         <v>999999</v>
@@ -10920,13 +10937,13 @@
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C26">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D26">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E26">
         <v>999999</v>
@@ -10937,13 +10954,13 @@
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C27">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D27">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E27">
         <v>999999</v>
@@ -10954,13 +10971,13 @@
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>58400</v>
+        <v>82.878395711488011</v>
       </c>
       <c r="C28">
-        <v>18000</v>
+        <v>18.98850500722336</v>
       </c>
       <c r="D28">
-        <v>21800</v>
+        <v>29.532863049035175</v>
       </c>
       <c r="E28">
         <v>999999</v>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A0B217-3077-4B04-8989-9088753CD6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C018DE9-0399-4D28-8BD4-9DD518F7785D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -9266,10 +9266,10 @@
         <v>5</v>
       </c>
       <c r="P3" s="6">
-        <v>126.83</v>
+        <v>118</v>
       </c>
       <c r="Q3" s="6">
-        <v>126.83</v>
+        <v>118</v>
       </c>
       <c r="R3" s="6">
         <v>0.95</v>
@@ -9349,10 +9349,10 @@
         <v>5</v>
       </c>
       <c r="P4" s="6">
-        <v>126.83</v>
+        <v>118</v>
       </c>
       <c r="Q4" s="6">
-        <v>126.83</v>
+        <v>118</v>
       </c>
       <c r="R4" s="6">
         <v>0.95</v>
@@ -10547,7 +10547,7 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B9" si="0">SUM(B3*1.04)</f>
+        <f t="shared" ref="B4:B8" si="0">SUM(B3*1.04)</f>
         <v>70844.800000000003</v>
       </c>
       <c r="C4">

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C018DE9-0399-4D28-8BD4-9DD518F7785D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76775CF2-2FE5-492A-BD98-4162FA4A53CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -544,7 +544,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -562,6 +562,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
@@ -9339,7 +9342,7 @@
       <c r="L4" s="5">
         <v>0.2</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="9">
         <v>20</v>
       </c>
       <c r="N4" s="5">

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F918984-D2CD-4EB7-B7E0-942DB386408D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F0D3AF-A98A-465D-816D-3782FCA9A9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="132">
   <si>
     <t>Value</t>
   </si>
@@ -400,9 +400,6 @@
     <t>Algeria</t>
   </si>
   <si>
-    <t>Nigeria</t>
-  </si>
-  <si>
     <t>Other Europe</t>
   </si>
   <si>
@@ -416,6 +413,33 @@
   </si>
   <si>
     <t>Other Americas</t>
+  </si>
+  <si>
+    <t>emissions</t>
+  </si>
+  <si>
+    <t>dummy block</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Oman</t>
+  </si>
+  <si>
+    <t>Other Asia Pacific</t>
+  </si>
+  <si>
+    <t>Other ME</t>
   </si>
 </sst>
 </file>
@@ -426,7 +450,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,6 +503,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -519,8 +549,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -602,7 +632,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
@@ -11030,9 +11062,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11046,19 +11079,25 @@
       <c r="C1" t="s">
         <v>116</v>
       </c>
+      <c r="D1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>138105619</v>
-      </c>
-      <c r="C2">
-        <v>1000</v>
+        <v>2126230105.0000002</v>
+      </c>
+      <c r="C2" s="8">
+        <v>13.655394085392276</v>
+      </c>
+      <c r="D2">
+        <v>4.9157999999999993E-2</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -11066,13 +11105,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>471381508</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
+        <v>1477077840.0000002</v>
+      </c>
+      <c r="C3" s="8">
+        <v>34.405314753080312</v>
+      </c>
+      <c r="D3">
+        <v>3.9239999999999997E-2</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -11080,13 +11122,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>27736037</v>
-      </c>
-      <c r="C4">
-        <v>1000</v>
+        <v>2321122320</v>
+      </c>
+      <c r="C4" s="8">
+        <v>23.606566326931016</v>
+      </c>
+      <c r="D4">
+        <v>0.19746</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -11094,13 +11139,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>61588793</v>
-      </c>
-      <c r="C5">
-        <v>1000</v>
+        <v>453673908.00000006</v>
+      </c>
+      <c r="C5" s="8">
+        <v>27.373571591866817</v>
+      </c>
+      <c r="D5">
+        <v>5.7239999999999999E-2</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -11108,13 +11156,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>144907263</v>
-      </c>
-      <c r="C6">
-        <v>1000</v>
+        <v>179359452.00000003</v>
+      </c>
+      <c r="C6" s="8">
+        <v>20.090694746324271</v>
+      </c>
+      <c r="D6">
+        <v>4.0806000000000002E-2</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -11122,13 +11173,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>471381508</v>
-      </c>
-      <c r="C7">
-        <v>1000</v>
+        <v>211011120.00000003</v>
+      </c>
+      <c r="C7" s="8">
+        <v>9.6058634255862909</v>
+      </c>
+      <c r="D7">
+        <v>6.9372000000000003E-2</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -11136,13 +11190,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>98828156</v>
-      </c>
-      <c r="C8">
-        <v>1000</v>
+        <v>397755961.20000005</v>
+      </c>
+      <c r="C8" s="8">
+        <v>27.656096986737001</v>
+      </c>
+      <c r="D8">
+        <v>5.7239999999999999E-2</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -11150,10 +11207,118 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>999999999999</v>
-      </c>
-      <c r="C9">
+        <v>167331818.16000003</v>
+      </c>
+      <c r="C9" s="8">
+        <v>17.48518277141034</v>
+      </c>
+      <c r="D9">
+        <v>4.4639999999999999E-2</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>220506620.40000001</v>
+      </c>
+      <c r="C10" s="8">
+        <v>34.405314753080312</v>
+      </c>
+      <c r="D10">
+        <v>5.7239999999999999E-2</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>90734781.600000009</v>
+      </c>
+      <c r="C11" s="8">
+        <v>18.175800403315236</v>
+      </c>
+      <c r="D11">
+        <v>4.6440000000000002E-2</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>633033360</v>
+      </c>
+      <c r="C12" s="8">
+        <v>25.709810933186837</v>
+      </c>
+      <c r="D12">
+        <v>5.1839999999999997E-2</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>81239281.200000003</v>
+      </c>
+      <c r="C13" s="8">
+        <v>15.664463560024705</v>
+      </c>
+      <c r="D13">
+        <v>4.4639999999999999E-2</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1055055600.0000001</v>
+      </c>
+      <c r="C14" s="8">
+        <v>18.866418035220136</v>
+      </c>
+      <c r="D14">
+        <v>4.4639999999999999E-2</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>99999999999</v>
+      </c>
+      <c r="C15">
         <v>1000</v>
+      </c>
+      <c r="D15">
+        <v>0.19746</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F0D3AF-A98A-465D-816D-3782FCA9A9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1294A14-454B-4C12-A610-4EBC208C09E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
@@ -23,6 +23,9 @@
     <sheet name="installable_capacity" sheetId="3" r:id="rId8"/>
     <sheet name="lng_block" sheetId="13" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">lng_block!$C$1:$C$15</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -632,7 +635,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9241,10 +9244,10 @@
         <v>0.38879999999999998</v>
       </c>
       <c r="K2" s="5">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L2" s="5">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="M2">
         <v>25</v>
@@ -9324,10 +9327,10 @@
         <v>0.2</v>
       </c>
       <c r="K3" s="5">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L3" s="5">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="M3">
         <v>20</v>
@@ -9407,10 +9410,10 @@
         <v>0.2</v>
       </c>
       <c r="K4" s="5">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L4" s="5">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="M4" s="9">
         <v>20</v>
@@ -9490,10 +9493,10 @@
         <v>0.3</v>
       </c>
       <c r="K5" s="5">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L5" s="5">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="M5">
         <v>30</v>
@@ -10713,11 +10716,9 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C9">
-        <f>SUM(C8*1.2465)</f>
-        <v>7865.415</v>
+        <v>7865.4149999999991</v>
       </c>
       <c r="D9">
-        <f>SUM(D8*1.0626)</f>
         <v>23164.68</v>
       </c>
       <c r="E9">
@@ -10732,11 +10733,9 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C10:C12" si="1">SUM(C9*1.2465)</f>
-        <v>9804.2397975000003</v>
+        <v>9804.2397974999967</v>
       </c>
       <c r="D10">
-        <f t="shared" ref="D10:D13" si="2">SUM(D9*1.0626)</f>
         <v>24614.788968000001</v>
       </c>
       <c r="E10">
@@ -10751,12 +10750,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C11">
-        <f t="shared" si="1"/>
-        <v>12220.98490758375</v>
+        <v>12220.984907583746</v>
       </c>
       <c r="D11">
-        <f t="shared" si="2"/>
-        <v>26155.674757396802</v>
+        <v>26155.674757396799</v>
       </c>
       <c r="E11">
         <v>999999</v>
@@ -10770,12 +10767,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C12">
-        <f t="shared" si="1"/>
-        <v>15233.457687303144</v>
+        <v>15233.457687303138</v>
       </c>
       <c r="D12">
-        <f t="shared" si="2"/>
-        <v>27793.019997209842</v>
+        <v>27793.019997209838</v>
       </c>
       <c r="E12">
         <v>999999</v>
@@ -10789,12 +10784,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C13">
-        <f>SUM(C12*1.2465)</f>
-        <v>18988.505007223368</v>
+        <v>18988.505007223361</v>
       </c>
       <c r="D13">
-        <f t="shared" si="2"/>
-        <v>29532.863049035179</v>
+        <v>29532.863049035175</v>
       </c>
       <c r="E13">
         <v>999999</v>
@@ -10808,10 +10801,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C14">
-        <v>18988.505007223368</v>
+        <v>20887.355507945696</v>
       </c>
       <c r="D14">
-        <v>29532.863049035179</v>
+        <v>29532.863049035175</v>
       </c>
       <c r="E14">
         <v>999999</v>
@@ -10825,10 +10818,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C15">
-        <v>18988.505007223368</v>
+        <v>22976.091058740265</v>
       </c>
       <c r="D15">
-        <v>29532.863049035179</v>
+        <v>29532.863049035175</v>
       </c>
       <c r="E15">
         <v>999999</v>
@@ -10842,10 +10835,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C16">
-        <v>18988.505007223368</v>
+        <v>25273.700164614293</v>
       </c>
       <c r="D16">
-        <v>29532.863049035179</v>
+        <v>29532.863049035175</v>
       </c>
       <c r="E16">
         <v>999999</v>
@@ -10859,10 +10852,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C17">
-        <v>18988.505007223368</v>
+        <v>27801.070181075727</v>
       </c>
       <c r="D17">
-        <v>29532.863049035179</v>
+        <v>29532.863049035175</v>
       </c>
       <c r="E17">
         <v>999999</v>
@@ -10876,10 +10869,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C18">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D18">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E18">
         <v>999999</v>
@@ -10893,10 +10886,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C19">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D19">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E19">
         <v>999999</v>
@@ -10910,10 +10903,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C20">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D20">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E20">
         <v>999999</v>
@@ -10927,10 +10920,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C21">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D21">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E21">
         <v>999999</v>
@@ -10944,10 +10937,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C22">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D22">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E22">
         <v>999999</v>
@@ -10961,10 +10954,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C23">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D23">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E23">
         <v>999999</v>
@@ -10978,10 +10971,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C24">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D24">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E24">
         <v>999999</v>
@@ -10995,10 +10988,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C25">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D25">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E25">
         <v>999999</v>
@@ -11012,10 +11005,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C26">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D26">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E26">
         <v>999999</v>
@@ -11029,10 +11022,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C27">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D27">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E27">
         <v>999999</v>
@@ -11046,10 +11039,10 @@
         <v>82878.395711488018</v>
       </c>
       <c r="C28">
-        <v>18988.505007223368</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="D28">
-        <v>29532.863049035179</v>
+        <v>30581.177199183301</v>
       </c>
       <c r="E28">
         <v>999999</v>
@@ -11088,16 +11081,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2126230105.0000002</v>
+        <v>211011120.00000003</v>
       </c>
       <c r="C2" s="8">
-        <v>13.655394085392276</v>
+        <v>9.61</v>
       </c>
       <c r="D2">
-        <v>4.9157999999999993E-2</v>
+        <v>6.9372000000000003E-2</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -11105,16 +11098,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1477077840.0000002</v>
+        <v>2126230105.0000002</v>
       </c>
       <c r="C3" s="8">
-        <v>34.405314753080312</v>
+        <v>13.66</v>
       </c>
       <c r="D3">
-        <v>3.9239999999999997E-2</v>
+        <v>4.9157999999999993E-2</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -11122,16 +11115,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2321122320</v>
+        <v>81239281.200000003</v>
       </c>
       <c r="C4" s="8">
-        <v>23.606566326931016</v>
+        <v>15.66</v>
       </c>
       <c r="D4">
-        <v>0.19746</v>
+        <v>4.4639999999999999E-2</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -11139,16 +11132,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>453673908.00000006</v>
+        <v>167331818.16000003</v>
       </c>
       <c r="C5" s="8">
-        <v>27.373571591866817</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="D5">
-        <v>5.7239999999999999E-2</v>
+        <v>4.4639999999999999E-2</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -11156,16 +11149,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>179359452.00000003</v>
+        <v>90734781.600000009</v>
       </c>
       <c r="C6" s="8">
-        <v>20.090694746324271</v>
+        <v>18.18</v>
       </c>
       <c r="D6">
-        <v>4.0806000000000002E-2</v>
+        <v>4.6440000000000002E-2</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -11173,16 +11166,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>211011120.00000003</v>
+        <v>1055055600.0000001</v>
       </c>
       <c r="C7" s="8">
-        <v>9.6058634255862909</v>
+        <v>18.87</v>
       </c>
       <c r="D7">
-        <v>6.9372000000000003E-2</v>
+        <v>4.4639999999999999E-2</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -11190,16 +11183,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>397755961.20000005</v>
+        <v>179359452.00000003</v>
       </c>
       <c r="C8" s="8">
-        <v>27.656096986737001</v>
+        <v>20.09</v>
       </c>
       <c r="D8">
-        <v>5.7239999999999999E-2</v>
+        <v>4.0806000000000002E-2</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -11207,16 +11200,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>167331818.16000003</v>
+        <v>2321122320</v>
       </c>
       <c r="C9" s="8">
-        <v>17.48518277141034</v>
+        <v>23.61</v>
       </c>
       <c r="D9">
-        <v>4.4639999999999999E-2</v>
+        <v>0.19746</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -11224,16 +11217,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>220506620.40000001</v>
+        <v>633033360</v>
       </c>
       <c r="C10" s="8">
-        <v>34.405314753080312</v>
+        <v>25.71</v>
       </c>
       <c r="D10">
-        <v>5.7239999999999999E-2</v>
+        <v>5.1839999999999997E-2</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -11241,16 +11234,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>90734781.600000009</v>
+        <v>453673908.00000006</v>
       </c>
       <c r="C11" s="8">
-        <v>18.175800403315236</v>
+        <v>27.37</v>
       </c>
       <c r="D11">
-        <v>4.6440000000000002E-2</v>
+        <v>5.7239999999999999E-2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -11258,16 +11251,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>633033360</v>
+        <v>397755961.20000005</v>
       </c>
       <c r="C12" s="8">
-        <v>25.709810933186837</v>
+        <v>27.66</v>
       </c>
       <c r="D12">
-        <v>5.1839999999999997E-2</v>
+        <v>5.7239999999999999E-2</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -11275,16 +11268,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>81239281.200000003</v>
+        <v>1477077840.0000002</v>
       </c>
       <c r="C13" s="8">
-        <v>15.664463560024705</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D13">
-        <v>4.4639999999999999E-2</v>
+        <v>3.9239999999999997E-2</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -11292,16 +11285,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1055055600.0000001</v>
+        <v>220506620.40000001</v>
       </c>
       <c r="C14" s="8">
-        <v>18.866418035220136</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D14">
-        <v>4.4639999999999999E-2</v>
+        <v>5.7239999999999999E-2</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242CF2B7-D5E0-4759-9FC3-53FB16E4A55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26DF181-503A-4DDD-9E5E-B3E89E525DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -11202,7 +11202,7 @@
       <c r="B9">
         <v>2321122320</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>23.61</v>
       </c>
       <c r="D9">
@@ -11219,7 +11219,7 @@
       <c r="B10">
         <v>633033360</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="8">
         <v>25.71</v>
       </c>
       <c r="D10">
@@ -11236,7 +11236,7 @@
       <c r="B11">
         <v>453673908.00000006</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="8">
         <v>27.37</v>
       </c>
       <c r="D11">
@@ -11253,7 +11253,7 @@
       <c r="B12">
         <v>397755961.20000005</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="8">
         <v>27.66</v>
       </c>
       <c r="D12">
@@ -11270,7 +11270,7 @@
       <c r="B13">
         <v>1477077840.0000002</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="8">
         <v>34.409999999999997</v>
       </c>
       <c r="D13">
@@ -11287,7 +11287,7 @@
       <c r="B14">
         <v>220506620.40000001</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="8">
         <v>34.409999999999997</v>
       </c>
       <c r="D14">
@@ -11304,7 +11304,7 @@
       <c r="B15">
         <v>99999999999</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="8">
         <v>1000</v>
       </c>
       <c r="D15">

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26DF181-503A-4DDD-9E5E-B3E89E525DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B802C3-58CC-41DB-9A14-CDBF4AD62AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="136">
   <si>
     <t>Value</t>
   </si>
@@ -443,6 +443,18 @@
   </si>
   <si>
     <t>Other ME</t>
+  </si>
+  <si>
+    <t>oandm_EU27_solarPV</t>
+  </si>
+  <si>
+    <t>oandm_EU27_windoff</t>
+  </si>
+  <si>
+    <t>oandm_EU27_windon</t>
+  </si>
+  <si>
+    <t>oandm_EU27_Batteries</t>
   </si>
 </sst>
 </file>
@@ -1023,26 +1035,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185AF38-42FD-4CFF-B287-2FCFFF6C6EF3}">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="37.33203125" customWidth="1"/>
-    <col min="5" max="5" width="29.88671875" customWidth="1"/>
-    <col min="6" max="6" width="39.88671875" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" customWidth="1"/>
-    <col min="9" max="9" width="22.5546875" customWidth="1"/>
-    <col min="10" max="10" width="24.109375" customWidth="1"/>
-    <col min="11" max="11" width="27.6640625" customWidth="1"/>
-    <col min="12" max="12" width="22.88671875" customWidth="1"/>
-    <col min="13" max="13" width="20.109375" customWidth="1"/>
-    <col min="15" max="15" width="32.6640625" customWidth="1"/>
-    <col min="16" max="16" width="35.33203125" customWidth="1"/>
-    <col min="17" max="17" width="31.44140625" customWidth="1"/>
+    <col min="4" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="29.88671875" customWidth="1"/>
+    <col min="7" max="7" width="39.88671875" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="10" max="11" width="22.5546875" customWidth="1"/>
+    <col min="12" max="12" width="24.109375" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" customWidth="1"/>
+    <col min="14" max="14" width="22.88671875" customWidth="1"/>
+    <col min="15" max="16" width="20.109375" customWidth="1"/>
+    <col min="18" max="18" width="32.6640625" customWidth="1"/>
+    <col min="19" max="19" width="35.33203125" customWidth="1"/>
+    <col min="20" max="20" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1059,43 +1071,55 @@
         <v>37</v>
       </c>
       <c r="F1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>30</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" t="s">
         <v>43</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>44</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>45</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>46</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q1" t="s">
         <v>52</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>53</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>54</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -1112,43 +1136,55 @@
         <v>1000</v>
       </c>
       <c r="F2" s="8">
+        <v>4400</v>
+      </c>
+      <c r="G2" s="8">
         <v>1775265.6417320003</v>
       </c>
-      <c r="G2" s="8">
+      <c r="H2" s="8">
         <v>2337972.5216000001</v>
       </c>
-      <c r="H2" s="8">
+      <c r="I2" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I2" s="8">
+      <c r="J2" s="8">
         <v>1000</v>
       </c>
-      <c r="J2" s="8">
+      <c r="K2" s="8">
+        <v>44000</v>
+      </c>
+      <c r="L2" s="8">
         <v>1052044.8400000001</v>
       </c>
-      <c r="K2" s="8">
+      <c r="M2" s="8">
         <v>1673707.7</v>
       </c>
-      <c r="L2" s="8">
+      <c r="N2" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>1000</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2">
+        <v>17386.633918245541</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="8">
+      <c r="S2" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q2">
+      <c r="T2">
         <v>1000</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1165,43 +1201,55 @@
         <v>1000</v>
       </c>
       <c r="F3" s="8">
+        <v>4400</v>
+      </c>
+      <c r="G3" s="8">
         <v>1722922.372057667</v>
       </c>
-      <c r="G3" s="8">
+      <c r="H3" s="8">
         <v>2318026.381866667</v>
       </c>
-      <c r="H3" s="8">
+      <c r="I3" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I3" s="8">
+      <c r="J3" s="8">
         <v>1000</v>
       </c>
-      <c r="J3" s="8">
+      <c r="K3" s="8">
+        <v>44000</v>
+      </c>
+      <c r="L3" s="8">
         <v>1042480.7960000001</v>
       </c>
-      <c r="K3" s="8">
+      <c r="M3" s="8">
         <v>1660955.6413333334</v>
       </c>
-      <c r="L3" s="8">
+      <c r="N3" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>1000</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="P3">
+        <v>17386.633918245541</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="P3" s="8">
+      <c r="S3" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q3">
+      <c r="T3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -1218,43 +1266,55 @@
         <v>1000</v>
       </c>
       <c r="F4" s="8">
+        <v>4400</v>
+      </c>
+      <c r="G4" s="8">
         <v>1670579.1023833335</v>
       </c>
-      <c r="G4" s="8">
+      <c r="H4" s="8">
         <v>2298080.2421333333</v>
       </c>
-      <c r="H4" s="8">
+      <c r="I4" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I4" s="8">
+      <c r="J4" s="8">
         <v>1000</v>
       </c>
-      <c r="J4" s="8">
+      <c r="K4" s="8">
+        <v>44000</v>
+      </c>
+      <c r="L4" s="8">
         <v>1032916.7520000001</v>
       </c>
-      <c r="K4" s="8">
+      <c r="M4" s="8">
         <v>1648203.5826666667</v>
       </c>
-      <c r="L4" s="8">
+      <c r="N4" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>1000</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="P4">
+        <v>17386.633918245541</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="P4" s="8">
+      <c r="S4" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q4">
+      <c r="T4">
         <v>1000</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -1271,43 +1331,55 @@
         <v>1000</v>
       </c>
       <c r="F5" s="8">
+        <v>4400</v>
+      </c>
+      <c r="G5" s="8">
         <v>1618235.832709</v>
       </c>
-      <c r="G5" s="8">
+      <c r="H5" s="8">
         <v>2278134.1023999997</v>
       </c>
-      <c r="H5" s="8">
+      <c r="I5" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I5" s="8">
+      <c r="J5" s="8">
         <v>1000</v>
       </c>
-      <c r="J5" s="8">
+      <c r="K5" s="8">
+        <v>44000</v>
+      </c>
+      <c r="L5" s="8">
         <v>1023352.708</v>
       </c>
-      <c r="K5" s="8">
+      <c r="M5" s="8">
         <v>1635451.524</v>
       </c>
-      <c r="L5" s="8">
+      <c r="N5" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>1000</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="P5">
+        <v>17386.633918245541</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P5" s="8">
+      <c r="S5" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q5">
+      <c r="T5">
         <v>1000</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -1324,43 +1396,55 @@
         <v>1000</v>
       </c>
       <c r="F6" s="8">
+        <v>4400</v>
+      </c>
+      <c r="G6" s="8">
         <v>1565892.5630346665</v>
       </c>
-      <c r="G6" s="8">
+      <c r="H6" s="8">
         <v>2258187.9626666661</v>
       </c>
-      <c r="H6" s="8">
+      <c r="I6" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I6" s="8">
+      <c r="J6" s="8">
         <v>1000</v>
       </c>
-      <c r="J6" s="8">
+      <c r="K6" s="8">
+        <v>44000</v>
+      </c>
+      <c r="L6" s="8">
         <v>1013788.6639999999</v>
       </c>
-      <c r="K6" s="8">
+      <c r="M6" s="8">
         <v>1622699.4653333335</v>
       </c>
-      <c r="L6" s="8">
+      <c r="N6" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>1000</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="P6">
+        <v>17386.633918245541</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="P6" s="8">
+      <c r="S6" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q6">
+      <c r="T6">
         <v>1000</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -1377,43 +1461,55 @@
         <v>1000</v>
       </c>
       <c r="F7" s="8">
+        <v>4400</v>
+      </c>
+      <c r="G7" s="8">
         <v>1513549.293360333</v>
       </c>
-      <c r="G7" s="8">
+      <c r="H7" s="8">
         <v>2238241.8229333302</v>
       </c>
-      <c r="H7" s="8">
+      <c r="I7" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I7" s="8">
+      <c r="J7" s="8">
         <v>1000</v>
       </c>
-      <c r="J7" s="8">
+      <c r="K7" s="8">
+        <v>44000</v>
+      </c>
+      <c r="L7" s="8">
         <v>1004224.62</v>
       </c>
-      <c r="K7" s="8">
+      <c r="M7" s="8">
         <v>1609947.4066666667</v>
       </c>
-      <c r="L7" s="8">
+      <c r="N7" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>1000</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="P7">
+        <v>17386.633918245541</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="P7" s="8">
+      <c r="S7" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q7">
+      <c r="T7">
         <v>1000</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -1430,43 +1526,55 @@
         <v>1000</v>
       </c>
       <c r="F8" s="8">
+        <v>3900</v>
+      </c>
+      <c r="G8" s="8">
         <v>1461206.0236859999</v>
       </c>
-      <c r="G8" s="8">
+      <c r="H8" s="8">
         <v>2218295.6831999999</v>
       </c>
-      <c r="H8" s="8">
+      <c r="I8" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I8" s="8">
+      <c r="J8" s="8">
         <v>1000</v>
       </c>
-      <c r="J8" s="8">
+      <c r="K8" s="8">
+        <v>34000</v>
+      </c>
+      <c r="L8" s="8">
         <v>994660.57600000012</v>
       </c>
-      <c r="K8" s="8">
+      <c r="M8" s="8">
         <v>1597195.3480000002</v>
       </c>
-      <c r="L8" s="8">
+      <c r="N8" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>1000</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="P8">
+        <v>16662.667964091612</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="P8" s="8">
+      <c r="S8" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q8">
+      <c r="T8">
         <v>1000</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -1483,43 +1591,55 @@
         <v>1000</v>
       </c>
       <c r="F9" s="8">
+        <v>3900</v>
+      </c>
+      <c r="G9" s="8">
         <v>1444015.15599508</v>
       </c>
-      <c r="G9" s="8">
+      <c r="H9" s="8">
         <v>2205259.4561600001</v>
       </c>
-      <c r="H9" s="8">
+      <c r="I9" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I9" s="8">
+      <c r="J9" s="8">
         <v>1000</v>
       </c>
-      <c r="J9" s="8">
+      <c r="K9" s="8">
+        <v>34000</v>
+      </c>
+      <c r="L9" s="8">
         <v>992747.76720000012</v>
       </c>
-      <c r="K9" s="8">
+      <c r="M9" s="8">
         <v>1594326.1348000003</v>
       </c>
-      <c r="L9" s="8">
+      <c r="N9" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>1000</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="P9">
+        <v>16662.667964091612</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="P9" s="8">
+      <c r="S9" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q9">
+      <c r="T9">
         <v>1000</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -1536,43 +1656,55 @@
         <v>1000</v>
       </c>
       <c r="F10" s="8">
+        <v>3900</v>
+      </c>
+      <c r="G10" s="8">
         <v>1426824.2883041599</v>
       </c>
-      <c r="G10" s="8">
+      <c r="H10" s="8">
         <v>2192223.2291199998</v>
       </c>
-      <c r="H10" s="8">
+      <c r="I10" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I10" s="8">
+      <c r="J10" s="8">
         <v>1000</v>
       </c>
-      <c r="J10" s="8">
+      <c r="K10" s="8">
+        <v>34000</v>
+      </c>
+      <c r="L10" s="8">
         <v>990834.9584</v>
       </c>
-      <c r="K10" s="8">
+      <c r="M10" s="8">
         <v>1591456.9216000002</v>
       </c>
-      <c r="L10" s="8">
+      <c r="N10" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>1000</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="P10">
+        <v>16662.667964091612</v>
+      </c>
+      <c r="Q10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P10" s="8">
+      <c r="S10" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q10">
+      <c r="T10">
         <v>1000</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -1589,43 +1721,55 @@
         <v>1000</v>
       </c>
       <c r="F11" s="8">
+        <v>3900</v>
+      </c>
+      <c r="G11" s="8">
         <v>1409633.42061324</v>
       </c>
-      <c r="G11" s="8">
+      <c r="H11" s="8">
         <v>2179187.0020799995</v>
       </c>
-      <c r="H11" s="8">
+      <c r="I11" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I11" s="8">
+      <c r="J11" s="8">
         <v>1000</v>
       </c>
-      <c r="J11" s="8">
+      <c r="K11" s="8">
+        <v>34000</v>
+      </c>
+      <c r="L11" s="8">
         <v>988922.1496</v>
       </c>
-      <c r="K11" s="8">
+      <c r="M11" s="8">
         <v>1588587.7084000004</v>
       </c>
-      <c r="L11" s="8">
+      <c r="N11" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>1000</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="P11">
+        <v>16662.667964091612</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="P11" s="8">
+      <c r="S11" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q11">
+      <c r="T11">
         <v>1000</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -1642,43 +1786,55 @@
         <v>1000</v>
       </c>
       <c r="F12" s="8">
+        <v>3900</v>
+      </c>
+      <c r="G12" s="8">
         <v>1392442.5529223196</v>
       </c>
-      <c r="G12" s="8">
+      <c r="H12" s="8">
         <v>2166150.7750399997</v>
       </c>
-      <c r="H12" s="8">
+      <c r="I12" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I12" s="8">
+      <c r="J12" s="8">
         <v>1000</v>
       </c>
-      <c r="J12" s="8">
+      <c r="K12" s="8">
+        <v>34000</v>
+      </c>
+      <c r="L12" s="8">
         <v>987009.34079999989</v>
       </c>
-      <c r="K12" s="8">
+      <c r="M12" s="8">
         <v>1585718.4952000002</v>
       </c>
-      <c r="L12" s="8">
+      <c r="N12" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>1000</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="P12">
+        <v>16662.667964091612</v>
+      </c>
+      <c r="Q12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="P12" s="8">
+      <c r="S12" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q12">
+      <c r="T12">
         <v>1000</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -1695,43 +1851,55 @@
         <v>1000</v>
       </c>
       <c r="F13" s="8">
+        <v>3900</v>
+      </c>
+      <c r="G13" s="8">
         <v>1375251.6852313997</v>
       </c>
-      <c r="G13" s="8">
+      <c r="H13" s="8">
         <v>2153114.5479999995</v>
       </c>
-      <c r="H13" s="8">
+      <c r="I13" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I13" s="8">
+      <c r="J13" s="8">
         <v>1000</v>
       </c>
-      <c r="J13" s="8">
+      <c r="K13" s="8">
+        <v>34000</v>
+      </c>
+      <c r="L13" s="8">
         <v>985096.53199999989</v>
       </c>
-      <c r="K13" s="8">
+      <c r="M13" s="8">
         <v>1582849.2820000004</v>
       </c>
-      <c r="L13" s="8">
+      <c r="N13" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>1000</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="P13">
+        <v>16662.667964091612</v>
+      </c>
+      <c r="Q13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="P13" s="8">
+      <c r="S13" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q13">
+      <c r="T13">
         <v>1000</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -1748,43 +1916,55 @@
         <v>1000</v>
       </c>
       <c r="F14" s="8">
+        <v>3900</v>
+      </c>
+      <c r="G14" s="8">
         <v>1358060.8175404796</v>
       </c>
-      <c r="G14" s="8">
+      <c r="H14" s="8">
         <v>2140078.3209599997</v>
       </c>
-      <c r="H14" s="8">
+      <c r="I14" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I14" s="8">
+      <c r="J14" s="8">
         <v>1000</v>
       </c>
-      <c r="J14" s="8">
+      <c r="K14" s="8">
+        <v>34000</v>
+      </c>
+      <c r="L14" s="8">
         <v>983183.72319999977</v>
       </c>
-      <c r="K14" s="8">
+      <c r="M14" s="8">
         <v>1579980.0688000005</v>
       </c>
-      <c r="L14" s="8">
+      <c r="N14" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>1000</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="P14">
+        <v>16662.667964091612</v>
+      </c>
+      <c r="Q14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="P14" s="8">
+      <c r="S14" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q14">
+      <c r="T14">
         <v>1000</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -1801,43 +1981,55 @@
         <v>1000</v>
       </c>
       <c r="F15" s="8">
+        <v>3900</v>
+      </c>
+      <c r="G15" s="8">
         <v>1340869.9498495597</v>
       </c>
-      <c r="G15" s="8">
+      <c r="H15" s="8">
         <v>2127042.0939199994</v>
       </c>
-      <c r="H15" s="8">
+      <c r="I15" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I15" s="8">
+      <c r="J15" s="8">
         <v>1000</v>
       </c>
-      <c r="J15" s="8">
+      <c r="K15" s="8">
+        <v>34000</v>
+      </c>
+      <c r="L15" s="8">
         <v>981270.91439999978</v>
       </c>
-      <c r="K15" s="8">
+      <c r="M15" s="8">
         <v>1577110.8556000004</v>
       </c>
-      <c r="L15" s="8">
+      <c r="N15" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>1000</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="P15">
+        <v>16662.667964091612</v>
+      </c>
+      <c r="Q15" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="P15" s="8">
+      <c r="S15" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q15">
+      <c r="T15">
         <v>1000</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -1854,43 +2046,55 @@
         <v>1000</v>
       </c>
       <c r="F16" s="8">
+        <v>3900</v>
+      </c>
+      <c r="G16" s="8">
         <v>1323679.0821586396</v>
       </c>
-      <c r="G16" s="8">
+      <c r="H16" s="8">
         <v>2114005.8668799992</v>
       </c>
-      <c r="H16" s="8">
+      <c r="I16" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I16" s="8">
+      <c r="J16" s="8">
         <v>1000</v>
       </c>
-      <c r="J16" s="8">
+      <c r="K16" s="8">
+        <v>34000</v>
+      </c>
+      <c r="L16" s="8">
         <v>979358.10559999966</v>
       </c>
-      <c r="K16" s="8">
+      <c r="M16" s="8">
         <v>1574241.6424000005</v>
       </c>
-      <c r="L16" s="8">
+      <c r="N16" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>1000</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="P16">
+        <v>16662.667964091612</v>
+      </c>
+      <c r="Q16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="P16" s="8">
+      <c r="S16" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q16">
+      <c r="T16">
         <v>1000</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -1907,43 +2111,55 @@
         <v>1000</v>
       </c>
       <c r="F17" s="8">
+        <v>3900</v>
+      </c>
+      <c r="G17" s="8">
         <v>1306488.2144677194</v>
       </c>
-      <c r="G17" s="8">
+      <c r="H17" s="8">
         <v>2100969.6398399994</v>
       </c>
-      <c r="H17" s="8">
+      <c r="I17" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I17" s="8">
+      <c r="J17" s="8">
         <v>1000</v>
       </c>
-      <c r="J17" s="8">
+      <c r="K17" s="8">
+        <v>34000</v>
+      </c>
+      <c r="L17" s="8">
         <v>977445.29679999966</v>
       </c>
-      <c r="K17" s="8">
+      <c r="M17" s="8">
         <v>1571372.4292000004</v>
       </c>
-      <c r="L17" s="8">
+      <c r="N17" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>1000</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="P17">
+        <v>16662.667964091612</v>
+      </c>
+      <c r="Q17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="R17" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="P17" s="8">
+      <c r="S17" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q17">
+      <c r="T17">
         <v>1000</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -1960,43 +2176,55 @@
         <v>1000</v>
       </c>
       <c r="F18" s="8">
+        <v>3100</v>
+      </c>
+      <c r="G18" s="8">
         <v>1288027.7959324</v>
       </c>
-      <c r="G18" s="8">
+      <c r="H18" s="8">
         <v>2087933.4128</v>
       </c>
-      <c r="H18" s="8">
+      <c r="I18" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I18" s="8">
+      <c r="J18" s="8">
         <v>1000</v>
       </c>
-      <c r="J18" s="8">
+      <c r="K18" s="8">
+        <v>30000</v>
+      </c>
+      <c r="L18" s="8">
         <v>975532.48799999955</v>
       </c>
-      <c r="K18" s="8">
+      <c r="M18" s="8">
         <v>1568503.2160000005</v>
       </c>
-      <c r="L18" s="8">
+      <c r="N18" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>1000</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="P18">
+        <v>15965.364846295015</v>
+      </c>
+      <c r="Q18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P18" s="8">
+      <c r="S18" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q18">
+      <c r="T18">
         <v>1000</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -2013,43 +2241,55 @@
         <v>1000</v>
       </c>
       <c r="F19" s="8">
+        <v>3100</v>
+      </c>
+      <c r="G19" s="8">
         <v>1288154.7510168403</v>
       </c>
-      <c r="G19" s="8">
+      <c r="H19" s="8">
         <v>2076927.41784</v>
       </c>
-      <c r="H19" s="8">
+      <c r="I19" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I19" s="8">
+      <c r="J19" s="8">
         <v>1000</v>
       </c>
-      <c r="J19" s="8">
+      <c r="K19" s="8">
+        <v>30000</v>
+      </c>
+      <c r="L19" s="8">
         <v>973619.67919999966</v>
       </c>
-      <c r="K19" s="8">
+      <c r="M19" s="8">
         <v>1565634.0028000006</v>
       </c>
-      <c r="L19" s="8">
+      <c r="N19" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>1000</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="P19">
+        <v>15965.364846295015</v>
+      </c>
+      <c r="Q19" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="R19" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="P19" s="8">
+      <c r="S19" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q19">
+      <c r="T19">
         <v>1000</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -2066,43 +2306,55 @@
         <v>1000</v>
       </c>
       <c r="F20" s="8">
+        <v>3100</v>
+      </c>
+      <c r="G20" s="8">
         <v>1288281.7061012802</v>
       </c>
-      <c r="G20" s="8">
+      <c r="H20" s="8">
         <v>2065921.4228800002</v>
       </c>
-      <c r="H20" s="8">
+      <c r="I20" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I20" s="8">
+      <c r="J20" s="8">
         <v>1000</v>
       </c>
-      <c r="J20" s="8">
+      <c r="K20" s="8">
+        <v>30000</v>
+      </c>
+      <c r="L20" s="8">
         <v>971706.87039999955</v>
       </c>
-      <c r="K20" s="8">
+      <c r="M20" s="8">
         <v>1562764.7896000005</v>
       </c>
-      <c r="L20" s="8">
+      <c r="N20" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>1000</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="P20">
+        <v>15965.364846295015</v>
+      </c>
+      <c r="Q20" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="P20" s="8">
+      <c r="S20" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q20">
+      <c r="T20">
         <v>1000</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -2119,43 +2371,55 @@
         <v>1000</v>
       </c>
       <c r="F21" s="8">
+        <v>3100</v>
+      </c>
+      <c r="G21" s="8">
         <v>1288408.6611857202</v>
       </c>
-      <c r="G21" s="8">
+      <c r="H21" s="8">
         <v>2054915.4279200002</v>
       </c>
-      <c r="H21" s="8">
+      <c r="I21" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I21" s="8">
+      <c r="J21" s="8">
         <v>1000</v>
       </c>
-      <c r="J21" s="8">
+      <c r="K21" s="8">
+        <v>30000</v>
+      </c>
+      <c r="L21" s="8">
         <v>969794.06159999955</v>
       </c>
-      <c r="K21" s="8">
+      <c r="M21" s="8">
         <v>1559895.5764000006</v>
       </c>
-      <c r="L21" s="8">
+      <c r="N21" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>1000</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="P21">
+        <v>15965.364846295015</v>
+      </c>
+      <c r="Q21" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="P21" s="8">
+      <c r="S21" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q21">
+      <c r="T21">
         <v>1000</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -2172,43 +2436,55 @@
         <v>1000</v>
       </c>
       <c r="F22" s="8">
+        <v>3100</v>
+      </c>
+      <c r="G22" s="8">
         <v>1288535.6162701603</v>
       </c>
-      <c r="G22" s="8">
+      <c r="H22" s="8">
         <v>2043909.4329600004</v>
       </c>
-      <c r="H22" s="8">
+      <c r="I22" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I22" s="8">
+      <c r="J22" s="8">
         <v>1000</v>
       </c>
-      <c r="J22" s="8">
+      <c r="K22" s="8">
+        <v>30000</v>
+      </c>
+      <c r="L22" s="8">
         <v>967881.25279999943</v>
       </c>
-      <c r="K22" s="8">
+      <c r="M22" s="8">
         <v>1557026.3632000005</v>
       </c>
-      <c r="L22" s="8">
+      <c r="N22" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>1000</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="P22">
+        <v>15965.364846295015</v>
+      </c>
+      <c r="Q22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="P22" s="8">
+      <c r="S22" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q22">
+      <c r="T22">
         <v>1000</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -2225,43 +2501,55 @@
         <v>1000</v>
       </c>
       <c r="F23" s="8">
+        <v>3100</v>
+      </c>
+      <c r="G23" s="8">
         <v>1288662.5713546001</v>
       </c>
-      <c r="G23" s="8">
+      <c r="H23" s="8">
         <v>2032903.4380000005</v>
       </c>
-      <c r="H23" s="8">
+      <c r="I23" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I23" s="8">
+      <c r="J23" s="8">
         <v>1000</v>
       </c>
-      <c r="J23" s="8">
+      <c r="K23" s="8">
+        <v>30000</v>
+      </c>
+      <c r="L23" s="8">
         <v>965968.44399999944</v>
       </c>
-      <c r="K23" s="8">
+      <c r="M23" s="8">
         <v>1554157.1500000006</v>
       </c>
-      <c r="L23" s="8">
+      <c r="N23" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>1000</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="P23">
+        <v>15965.364846295015</v>
+      </c>
+      <c r="Q23" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="P23" s="8">
+      <c r="S23" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q23">
+      <c r="T23">
         <v>1000</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -2278,43 +2566,55 @@
         <v>1000</v>
       </c>
       <c r="F24" s="8">
+        <v>3100</v>
+      </c>
+      <c r="G24" s="8">
         <v>1288789.5264390404</v>
       </c>
-      <c r="G24" s="8">
+      <c r="H24" s="8">
         <v>2021897.4430400007</v>
       </c>
-      <c r="H24" s="8">
+      <c r="I24" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I24" s="8">
+      <c r="J24" s="8">
         <v>1000</v>
       </c>
-      <c r="J24" s="8">
+      <c r="K24" s="8">
+        <v>30000</v>
+      </c>
+      <c r="L24" s="8">
         <v>964055.63519999932</v>
       </c>
-      <c r="K24" s="8">
+      <c r="M24" s="8">
         <v>1551287.9368000007</v>
       </c>
-      <c r="L24" s="8">
+      <c r="N24" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>1000</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="P24">
+        <v>15965.364846295015</v>
+      </c>
+      <c r="Q24" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="R24" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="P24" s="8">
+      <c r="S24" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q24">
+      <c r="T24">
         <v>1000</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -2331,43 +2631,55 @@
         <v>1000</v>
       </c>
       <c r="F25" s="8">
+        <v>3100</v>
+      </c>
+      <c r="G25" s="8">
         <v>1288916.4815234803</v>
       </c>
-      <c r="G25" s="8">
+      <c r="H25" s="8">
         <v>2010891.4480800009</v>
       </c>
-      <c r="H25" s="8">
+      <c r="I25" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I25" s="8">
+      <c r="J25" s="8">
         <v>1000</v>
       </c>
-      <c r="J25" s="8">
+      <c r="K25" s="8">
+        <v>30000</v>
+      </c>
+      <c r="L25" s="8">
         <v>962142.82639999932</v>
       </c>
-      <c r="K25" s="8">
+      <c r="M25" s="8">
         <v>1548418.7236000006</v>
       </c>
-      <c r="L25" s="8">
+      <c r="N25" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>1000</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="P25">
+        <v>15965.364846295015</v>
+      </c>
+      <c r="Q25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="P25" s="8">
+      <c r="S25" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q25">
+      <c r="T25">
         <v>1000</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -2384,43 +2696,55 @@
         <v>1000</v>
       </c>
       <c r="F26" s="8">
+        <v>3100</v>
+      </c>
+      <c r="G26" s="8">
         <v>1289043.4366079206</v>
       </c>
-      <c r="G26" s="8">
+      <c r="H26" s="8">
         <v>1999885.4531200009</v>
       </c>
-      <c r="H26" s="8">
+      <c r="I26" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I26" s="8">
+      <c r="J26" s="8">
         <v>1000</v>
       </c>
-      <c r="J26" s="8">
+      <c r="K26" s="8">
+        <v>30000</v>
+      </c>
+      <c r="L26" s="8">
         <v>960230.01759999921</v>
       </c>
-      <c r="K26" s="8">
+      <c r="M26" s="8">
         <v>1545549.5104000007</v>
       </c>
-      <c r="L26" s="8">
+      <c r="N26" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>1000</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="P26">
+        <v>15965.364846295015</v>
+      </c>
+      <c r="Q26" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="R26" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="P26" s="8">
+      <c r="S26" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q26">
+      <c r="T26">
         <v>1000</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -2437,43 +2761,55 @@
         <v>1000</v>
       </c>
       <c r="F27" s="8">
+        <v>3100</v>
+      </c>
+      <c r="G27" s="8">
         <v>1289170.3916923604</v>
       </c>
-      <c r="G27" s="8">
+      <c r="H27" s="8">
         <v>1988879.4581600011</v>
       </c>
-      <c r="H27" s="8">
+      <c r="I27" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I27" s="8">
+      <c r="J27" s="8">
         <v>1000</v>
       </c>
-      <c r="J27" s="8">
+      <c r="K27" s="8">
+        <v>30000</v>
+      </c>
+      <c r="L27" s="8">
         <v>958317.20879999921</v>
       </c>
-      <c r="K27" s="8">
+      <c r="M27" s="8">
         <v>1542680.2972000006</v>
       </c>
-      <c r="L27" s="8">
+      <c r="N27" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>1000</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="P27">
+        <v>15965.364846295015</v>
+      </c>
+      <c r="Q27" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="R27" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="P27" s="8">
+      <c r="S27" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q27">
+      <c r="T27">
         <v>1000</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="U27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -2490,40 +2826,52 @@
         <v>1000</v>
       </c>
       <c r="F28" s="8">
+        <v>2500</v>
+      </c>
+      <c r="G28" s="8">
         <v>1289297.3467768</v>
       </c>
-      <c r="G28" s="8">
+      <c r="H28" s="8">
         <v>1977873.4631999999</v>
       </c>
-      <c r="H28" s="8">
+      <c r="I28" s="8">
         <v>1646946.1610000001</v>
       </c>
-      <c r="I28" s="8">
+      <c r="J28" s="8">
         <v>1000</v>
       </c>
-      <c r="J28" s="8">
+      <c r="K28" s="8">
+        <v>28000</v>
+      </c>
+      <c r="L28" s="8">
         <v>956404.40000000026</v>
       </c>
-      <c r="K28" s="8">
+      <c r="M28" s="8">
         <v>1539811.0840000003</v>
       </c>
-      <c r="L28" s="8">
+      <c r="N28" s="8">
         <v>1093231.041</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>1000</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="P28">
+        <v>15602.06928231802</v>
+      </c>
+      <c r="Q28" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="R28" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="P28" s="8">
+      <c r="S28" s="8">
         <v>489061.86</v>
       </c>
-      <c r="Q28">
+      <c r="T28">
         <v>1000</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAB626C-FF8B-49DC-9212-F08D6DF01308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3966CB-6233-4861-A1AB-524FA1662BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="gas_block" sheetId="13" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$C$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$B$1:$B$109</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -446,7 +446,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -474,7 +474,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -491,28 +490,7 @@
     <cellStyle name="N_Table1_Header" xfId="6" xr:uid="{5B945886-E1B9-4000-BFBC-F4E856A0CA51}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -9414,7 +9392,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="11">
-        <v>304000</v>
+        <v>211115</v>
       </c>
       <c r="C2" s="6">
         <v>40000</v>
@@ -9435,7 +9413,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="6">
-        <v>0.37409999999999999</v>
+        <v>0.24030000000000001</v>
       </c>
       <c r="J2" s="6">
         <v>0.38879999999999998</v>
@@ -9512,7 +9490,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="6">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -9580,7 +9558,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="7">
-        <v>210000</v>
+        <v>195370</v>
       </c>
       <c r="C4" s="7">
         <v>0</v>
@@ -9595,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="6">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -11254,16 +11232,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>62</v>
       </c>
       <c r="G1" s="10" t="s">
@@ -11271,16 +11249,16 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12">
+      <c r="A2" s="13">
         <v>2024</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2">
         <v>29.19</v>
       </c>
       <c r="G2" s="10">
@@ -11288,14 +11266,14 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D3" s="13">
+      <c r="C3" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D3">
         <v>42.69</v>
       </c>
       <c r="G3" s="10">
@@ -11303,14 +11281,14 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="C4" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D4">
         <v>150</v>
       </c>
       <c r="G4" s="10">
@@ -11318,1339 +11296,1320 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="13"/>
+      <c r="B5" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="13">
-        <v>319200000</v>
-      </c>
-      <c r="D5" s="13">
+      <c r="C5" s="2">
+        <v>532000000</v>
+      </c>
+      <c r="D5">
         <v>22.68</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>2025</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6">
         <v>29.19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="14" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D7" s="13">
+      <c r="C7" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D7">
         <v>42.69</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="14" t="s">
+      <c r="A8" s="13"/>
+      <c r="B8" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D8" s="13">
+      <c r="C8" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D8">
         <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="14" t="s">
+      <c r="A9" s="13"/>
+      <c r="B9" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="13">
-        <v>306266016</v>
-      </c>
-      <c r="D9" s="13">
+      <c r="C9" s="2">
+        <v>510132160</v>
+      </c>
+      <c r="D9">
         <v>22.545000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>2026</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10">
         <v>29.19</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="14" t="s">
+      <c r="A11" s="13"/>
+      <c r="B11" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D11" s="13">
+      <c r="C11" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D11">
         <v>42.69</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="13"/>
+      <c r="B12" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D12" s="13">
+      <c r="C12" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D12">
         <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="13"/>
+      <c r="B13" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="13">
-        <v>293856117.03167999</v>
-      </c>
-      <c r="D13" s="13">
+      <c r="C13" s="2">
+        <v>489197947</v>
+      </c>
+      <c r="D13">
         <v>22.41</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
+      <c r="A14" s="13">
         <v>2027</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14">
         <v>29.19</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="14" t="s">
+      <c r="A15" s="13"/>
+      <c r="B15" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D15">
         <v>42.69</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="13"/>
+      <c r="B16" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="C16" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D16">
         <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="13"/>
+      <c r="B17" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="13">
-        <v>281949067.16955632</v>
-      </c>
-      <c r="D17" s="13">
+      <c r="C17" s="2">
+        <v>469163758</v>
+      </c>
+      <c r="D17">
         <v>22.274999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
+      <c r="A18" s="13">
         <v>2028</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18">
         <v>29.19</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="13"/>
+      <c r="B19" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D19" s="13">
+      <c r="C19" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D19">
         <v>42.69</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="14" t="s">
+      <c r="A20" s="13"/>
+      <c r="B20" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D20" s="13">
+      <c r="C20" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D20">
         <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="13"/>
+      <c r="B21" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="13">
-        <v>270524490.96784592</v>
-      </c>
-      <c r="D21" s="13">
+      <c r="C21" s="2">
+        <v>449997786</v>
+      </c>
+      <c r="D21">
         <v>22.14</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="12">
+      <c r="A22" s="13">
         <v>2029</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22">
         <v>29.19</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="14" t="s">
+      <c r="A23" s="13"/>
+      <c r="B23" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D23" s="13">
+      <c r="C23" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D23">
         <v>42.69</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="13"/>
+      <c r="B24" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D24" s="13">
+      <c r="C24" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D24">
         <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="14" t="s">
+      <c r="A25" s="13"/>
+      <c r="B25" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="13">
-        <v>259562838.5938288</v>
-      </c>
-      <c r="D25" s="13">
+      <c r="C25" s="2">
+        <v>431671839</v>
+      </c>
+      <c r="D25">
         <v>22.004999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="12">
+      <c r="A26" s="13">
         <v>2030</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26">
         <v>29.19</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="12"/>
-      <c r="B27" s="14" t="s">
+      <c r="A27" s="13"/>
+      <c r="B27" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D27" s="13">
+      <c r="C27" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D27">
         <v>42.69</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="12"/>
-      <c r="B28" s="14" t="s">
+      <c r="A28" s="13"/>
+      <c r="B28" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D28" s="13">
+      <c r="C28" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D28">
         <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="12"/>
-      <c r="B29" s="14" t="s">
+      <c r="A29" s="13"/>
+      <c r="B29" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="13">
-        <v>249045352.37400681</v>
-      </c>
-      <c r="D29" s="13">
+      <c r="C29" s="2">
+        <v>414151522</v>
+      </c>
+      <c r="D29">
         <v>21.87</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="12">
+      <c r="A30" s="13">
         <v>2031</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30">
         <v>29.19</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="12"/>
-      <c r="B31" s="14" t="s">
+      <c r="A31" s="13"/>
+      <c r="B31" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D31" s="13">
+      <c r="C31" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D31">
         <v>42.69</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="12"/>
-      <c r="B32" s="14" t="s">
+      <c r="A32" s="13"/>
+      <c r="B32" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D32" s="13">
+      <c r="C32" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D32">
         <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="12"/>
-      <c r="B33" s="14" t="s">
+      <c r="A33" s="13"/>
+      <c r="B33" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="13">
-        <v>238954034.69581211</v>
-      </c>
-      <c r="D33" s="13">
+      <c r="C33" s="2">
+        <v>397404638</v>
+      </c>
+      <c r="D33">
         <v>21.734999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="12">
+      <c r="A34" s="13">
         <v>2032</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34">
         <v>29.19</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="12"/>
-      <c r="B35" s="14" t="s">
+      <c r="A35" s="13"/>
+      <c r="B35" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D35" s="13">
+      <c r="C35" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D35">
         <v>42.69</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="12"/>
-      <c r="B36" s="14" t="s">
+      <c r="A36" s="13"/>
+      <c r="B36" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D36" s="13">
+      <c r="C36" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D36">
         <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="12"/>
-      <c r="B37" s="14" t="s">
+      <c r="A37" s="13"/>
+      <c r="B37" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="13">
-        <v>229271617.20993781</v>
-      </c>
-      <c r="D37" s="13">
+      <c r="C37" s="2">
+        <v>381406956</v>
+      </c>
+      <c r="D37">
         <v>21.6</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="12">
+      <c r="A38" s="13">
         <v>2033</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38">
         <v>29.19</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="12"/>
-      <c r="B39" s="14" t="s">
+      <c r="A39" s="13"/>
+      <c r="B39" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C39" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D39" s="13">
+      <c r="C39" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D39">
         <v>42.69</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="14" t="s">
+      <c r="A40" s="13"/>
+      <c r="B40" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C40" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D40" s="13">
+      <c r="C40" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D40">
         <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="12"/>
-      <c r="B41" s="14" t="s">
+      <c r="A41" s="13"/>
+      <c r="B41" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="13">
-        <v>219981531.2805911</v>
-      </c>
-      <c r="D41" s="13">
+      <c r="C41" s="2">
+        <v>366136021</v>
+      </c>
+      <c r="D41">
         <v>21.465</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="12">
+      <c r="A42" s="13">
         <v>2034</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="13">
+      <c r="C42" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42">
         <v>29.19</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="12"/>
-      <c r="B43" s="14" t="s">
+      <c r="A43" s="13"/>
+      <c r="B43" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D43" s="13">
+      <c r="C43" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D43">
         <v>42.69</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="12"/>
-      <c r="B44" s="14" t="s">
+      <c r="A44" s="13"/>
+      <c r="B44" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C44" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D44" s="13">
+      <c r="C44" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D44">
         <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="12"/>
-      <c r="B45" s="14" t="s">
+      <c r="A45" s="13"/>
+      <c r="B45" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="13">
-        <v>211067879.63310149</v>
-      </c>
-      <c r="D45" s="13">
+      <c r="C45" s="2">
+        <v>351566712</v>
+      </c>
+      <c r="D45">
         <v>21.33</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="12">
+      <c r="A46" s="13">
         <v>2035</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="13">
+      <c r="C46" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D46" s="13">
+      <c r="D46">
         <v>29.19</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="12"/>
-      <c r="B47" s="14" t="s">
+      <c r="A47" s="13"/>
+      <c r="B47" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D47" s="13">
+      <c r="C47" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D47">
         <v>42.69</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
-      <c r="B48" s="14" t="s">
+      <c r="A48" s="13"/>
+      <c r="B48" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C48" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D48" s="13">
+      <c r="C48" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D48">
         <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="12"/>
-      <c r="B49" s="14" t="s">
+      <c r="A49" s="13"/>
+      <c r="B49" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C49" s="13">
-        <v>202515409.1503683</v>
-      </c>
-      <c r="D49" s="13">
+      <c r="C49" s="2">
+        <v>337680248</v>
+      </c>
+      <c r="D49">
         <v>21.195</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="12">
+      <c r="A50" s="13">
         <v>2036</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="13">
+      <c r="C50" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D50" s="13">
+      <c r="D50">
         <v>29.19</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
-      <c r="B51" s="14" t="s">
+      <c r="A51" s="13"/>
+      <c r="B51" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C51" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D51" s="13">
+      <c r="C51" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D51">
         <v>42.69</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="12"/>
-      <c r="B52" s="14" t="s">
+      <c r="A52" s="13"/>
+      <c r="B52" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C52" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D52" s="13">
+      <c r="C52" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D52">
         <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="12"/>
-      <c r="B53" s="14" t="s">
+      <c r="A53" s="13"/>
+      <c r="B53" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C53" s="13">
-        <v>194309484.77159539</v>
-      </c>
-      <c r="D53" s="13">
+      <c r="C53" s="2">
+        <v>324452734</v>
+      </c>
+      <c r="D53">
         <v>21.06</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="12">
+      <c r="A54" s="13">
         <v>2037</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="13">
+      <c r="C54" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D54" s="13">
+      <c r="D54">
         <v>29.19</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="12"/>
-      <c r="B55" s="14" t="s">
+      <c r="A55" s="13"/>
+      <c r="B55" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D55" s="13">
+      <c r="C55" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D55">
         <v>42.69</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="12"/>
-      <c r="B56" s="14" t="s">
+      <c r="A56" s="13"/>
+      <c r="B56" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C56" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D56" s="13">
+      <c r="C56" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D56">
         <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="12"/>
-      <c r="B57" s="14" t="s">
+      <c r="A57" s="13"/>
+      <c r="B57" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C57" s="13">
-        <v>186436064.4486503</v>
-      </c>
-      <c r="D57" s="13">
+      <c r="C57" s="2">
+        <v>311864566</v>
+      </c>
+      <c r="D57">
         <v>20.925000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="12">
+      <c r="A58" s="13">
         <v>2038</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C58" s="13">
+      <c r="C58" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D58" s="13">
+      <c r="D58">
         <v>29.19</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="12"/>
-      <c r="B59" s="14" t="s">
+      <c r="A59" s="13"/>
+      <c r="B59" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D59" s="13">
+      <c r="C59" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D59">
         <v>42.69</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="12"/>
-      <c r="B60" s="14" t="s">
+      <c r="A60" s="13"/>
+      <c r="B60" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D60" s="13">
+      <c r="C60" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D60">
         <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="12"/>
-      <c r="B61" s="14" t="s">
+      <c r="A61" s="13"/>
+      <c r="B61" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C61" s="13">
-        <v>178881675.11719099</v>
-      </c>
-      <c r="D61" s="13">
+      <c r="C61" s="2">
+        <v>299896970</v>
+      </c>
+      <c r="D61">
         <v>20.79</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="12">
+      <c r="A62" s="13">
         <v>2039</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C62" s="13">
+      <c r="C62" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D62" s="13">
+      <c r="D62">
         <v>29.19</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="12"/>
-      <c r="B63" s="14" t="s">
+      <c r="A63" s="13"/>
+      <c r="B63" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C63" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D63" s="13">
+      <c r="C63" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D63">
         <v>42.69</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="12"/>
-      <c r="B64" s="14" t="s">
+      <c r="A64" s="13"/>
+      <c r="B64" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C64" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D64" s="13">
+      <c r="C64" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D64">
         <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="12"/>
-      <c r="B65" s="14" t="s">
+      <c r="A65" s="13"/>
+      <c r="B65" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C65" s="13">
-        <v>171633389.64144239</v>
-      </c>
-      <c r="D65" s="13">
+      <c r="C65" s="2">
+        <v>288530884</v>
+      </c>
+      <c r="D65">
         <v>20.655000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="12">
+      <c r="A66" s="13">
         <v>2040</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C66" s="13">
+      <c r="C66" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D66" s="13">
+      <c r="D66">
         <v>29.19</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
-      <c r="B67" s="14" t="s">
+      <c r="A67" s="13"/>
+      <c r="B67" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C67" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D67" s="13">
+      <c r="C67" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D67">
         <v>42.69</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="12"/>
-      <c r="B68" s="14" t="s">
+      <c r="A68" s="13"/>
+      <c r="B68" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C68" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D68" s="13">
+      <c r="C68" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D68">
         <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="12"/>
-      <c r="B69" s="14" t="s">
+      <c r="A69" s="13"/>
+      <c r="B69" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C69" s="13">
-        <v>164678804.6931712</v>
-      </c>
-      <c r="D69" s="13">
+      <c r="C69" s="2">
+        <v>277748804</v>
+      </c>
+      <c r="D69">
         <v>20.52</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="12">
+      <c r="A70" s="13">
         <v>2041</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="13">
+      <c r="C70" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D70" s="13">
+      <c r="D70">
         <v>29.19</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="12"/>
-      <c r="B71" s="14" t="s">
+      <c r="A71" s="13"/>
+      <c r="B71" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C71" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D71" s="13">
+      <c r="C71" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D71">
         <v>42.69</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="12"/>
-      <c r="B72" s="14" t="s">
+      <c r="A72" s="13"/>
+      <c r="B72" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C72" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D72" s="13">
+      <c r="C72" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D72">
         <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="12"/>
-      <c r="B73" s="14" t="s">
+      <c r="A73" s="13"/>
+      <c r="B73" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C73" s="13">
-        <v>158006019.52700391</v>
-      </c>
-      <c r="D73" s="13">
+      <c r="C73" s="2">
+        <v>267535969</v>
+      </c>
+      <c r="D73">
         <v>20.52</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="12">
+      <c r="A74" s="13">
         <v>2042</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C74" s="13">
+      <c r="C74" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D74" s="13">
+      <c r="D74">
         <v>29.19</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="12"/>
-      <c r="B75" s="14" t="s">
+      <c r="A75" s="13"/>
+      <c r="B75" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C75" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D75" s="13">
+      <c r="C75" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D75">
         <v>42.69</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="12"/>
-      <c r="B76" s="14" t="s">
+      <c r="A76" s="13"/>
+      <c r="B76" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C76" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D76" s="13">
+      <c r="C76" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D76">
         <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="12"/>
-      <c r="B77" s="14" t="s">
+      <c r="A77" s="13"/>
+      <c r="B77" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C77" s="13">
-        <v>151603615.61576971</v>
-      </c>
-      <c r="D77" s="13">
+      <c r="C77" s="2">
+        <v>257872875</v>
+      </c>
+      <c r="D77">
         <v>20.52</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="12">
+      <c r="A78" s="13">
         <v>2043</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C78" s="13">
+      <c r="C78" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D78" s="13">
+      <c r="D78">
         <v>29.19</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="12"/>
-      <c r="B79" s="14" t="s">
+      <c r="A79" s="13"/>
+      <c r="B79" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C79" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D79" s="13">
+      <c r="C79" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D79">
         <v>42.69</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="12"/>
-      <c r="B80" s="14" t="s">
+      <c r="A80" s="13"/>
+      <c r="B80" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C80" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D80" s="13">
+      <c r="C80" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D80">
         <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="12"/>
-      <c r="B81" s="14" t="s">
+      <c r="A81" s="13"/>
+      <c r="B81" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C81" s="13">
-        <v>145460637.11101869</v>
-      </c>
-      <c r="D81" s="13">
+      <c r="C81" s="2">
+        <v>248744486</v>
+      </c>
+      <c r="D81">
         <v>20.52</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="12">
+      <c r="A82" s="13">
         <v>2044</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C82" s="13">
+      <c r="C82" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D82" s="13">
+      <c r="D82">
         <v>29.19</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="12"/>
-      <c r="B83" s="14" t="s">
+      <c r="A83" s="13"/>
+      <c r="B83" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C83" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D83" s="13">
+      <c r="C83" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D83">
         <v>42.69</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="12"/>
-      <c r="B84" s="14" t="s">
+      <c r="A84" s="13"/>
+      <c r="B84" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C84" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D84" s="13">
+      <c r="C84" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D84">
         <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="12"/>
-      <c r="B85" s="14" t="s">
+      <c r="A85" s="13"/>
+      <c r="B85" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C85" s="13">
-        <v>139566572.0952802</v>
-      </c>
-      <c r="D85" s="13">
+      <c r="C85" s="2">
+        <v>240136226</v>
+      </c>
+      <c r="D85">
         <v>20.52</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="12">
+      <c r="A86" s="13">
         <v>2045</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C86" s="13">
+      <c r="C86" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D86" s="13">
+      <c r="D86">
         <v>29.19</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="12"/>
-      <c r="B87" s="14" t="s">
+      <c r="A87" s="13"/>
+      <c r="B87" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C87" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D87" s="13">
+      <c r="C87" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D87">
         <v>42.69</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="12"/>
-      <c r="B88" s="14" t="s">
+      <c r="A88" s="13"/>
+      <c r="B88" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C88" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D88" s="13">
+      <c r="C88" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D88">
         <v>150</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="12"/>
-      <c r="B89" s="14" t="s">
+      <c r="A89" s="13"/>
+      <c r="B89" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C89" s="13">
-        <v>133911334.5939794</v>
-      </c>
-      <c r="D89" s="13">
+      <c r="C89" s="2">
+        <v>232032192</v>
+      </c>
+      <c r="D89">
         <v>20.52</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="12">
+      <c r="A90" s="13">
         <v>2046</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C90" s="13">
+      <c r="C90" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D90" s="13">
+      <c r="D90">
         <v>29.19</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="12"/>
-      <c r="B91" s="14" t="s">
+      <c r="A91" s="13"/>
+      <c r="B91" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C91" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D91" s="13">
+      <c r="C91" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D91">
         <v>42.69</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="12"/>
-      <c r="B92" s="14" t="s">
+      <c r="A92" s="13"/>
+      <c r="B92" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C92" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D92" s="13">
+      <c r="C92" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D92">
         <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="12"/>
-      <c r="B93" s="14" t="s">
+      <c r="A93" s="13"/>
+      <c r="B93" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C93" s="13">
-        <v>128485247.3162314</v>
-      </c>
-      <c r="D93" s="13">
+      <c r="C93" s="2">
+        <v>224418473</v>
+      </c>
+      <c r="D93">
         <v>20.52</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="12">
+      <c r="A94" s="13">
         <v>2047</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B94" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C94" s="13">
+      <c r="C94" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D94" s="13">
+      <c r="D94">
         <v>29.19</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="12"/>
-      <c r="B95" s="14" t="s">
+      <c r="A95" s="13"/>
+      <c r="B95" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C95" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D95" s="13">
+      <c r="C95" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D95">
         <v>42.69</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="12"/>
-      <c r="B96" s="14" t="s">
+      <c r="A96" s="13"/>
+      <c r="B96" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C96" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D96" s="13">
+      <c r="C96" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D96">
         <v>150</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="12"/>
-      <c r="B97" s="14" t="s">
+      <c r="A97" s="13"/>
+      <c r="B97" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C97" s="13">
-        <v>123279025.09497771</v>
-      </c>
-      <c r="D97" s="13">
+      <c r="C97" s="2">
+        <v>217272367</v>
+      </c>
+      <c r="D97">
         <v>20.52</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="12">
+      <c r="A98" s="13">
         <v>2048</v>
       </c>
-      <c r="B98" s="14" t="s">
+      <c r="B98" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C98" s="13">
+      <c r="C98" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D98" s="13">
+      <c r="D98">
         <v>29.19</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="12"/>
-      <c r="B99" s="14" t="s">
+      <c r="A99" s="13"/>
+      <c r="B99" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C99" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D99" s="13">
+      <c r="C99" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D99">
         <v>42.69</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="12"/>
-      <c r="B100" s="14" t="s">
+      <c r="A100" s="13"/>
+      <c r="B100" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C100" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D100" s="13">
+      <c r="C100" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D100">
         <v>150</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="12"/>
-      <c r="B101" s="14" t="s">
+      <c r="A101" s="13"/>
+      <c r="B101" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C101" s="13">
-        <v>118283758.9981292</v>
-      </c>
-      <c r="D101" s="13">
+      <c r="C101" s="2">
+        <v>210579168</v>
+      </c>
+      <c r="D101">
         <v>20.52</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="12">
+      <c r="A102" s="13">
         <v>2049</v>
       </c>
-      <c r="B102" s="14" t="s">
+      <c r="B102" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C102" s="13">
+      <c r="C102" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D102" s="13">
+      <c r="D102">
         <v>29.19</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="12"/>
-      <c r="B103" s="14" t="s">
+      <c r="A103" s="13"/>
+      <c r="B103" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C103" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D103" s="13">
+      <c r="C103" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D103">
         <v>42.69</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="12"/>
-      <c r="B104" s="14" t="s">
+      <c r="A104" s="13"/>
+      <c r="B104" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C104" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D104" s="13">
+      <c r="C104" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D104">
         <v>150</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="12"/>
-      <c r="B105" s="14" t="s">
+      <c r="A105" s="13"/>
+      <c r="B105" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C105" s="13">
-        <v>113490901.083525</v>
-      </c>
-      <c r="D105" s="13">
+      <c r="C105" s="2">
+        <v>204325995</v>
+      </c>
+      <c r="D105">
         <v>20.52</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="12">
+      <c r="A106" s="13">
         <v>2050</v>
       </c>
-      <c r="B106" s="14" t="s">
+      <c r="B106" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C106" s="13">
+      <c r="C106" s="2">
         <v>270613611.10000002</v>
       </c>
-      <c r="D106" s="13">
+      <c r="D106">
         <v>29.19</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="12"/>
-      <c r="B107" s="14" t="s">
+      <c r="A107" s="13"/>
+      <c r="B107" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C107" s="13">
-        <v>1047284444.4400001</v>
-      </c>
-      <c r="D107" s="13">
+      <c r="C107" s="2">
+        <v>1047284444</v>
+      </c>
+      <c r="D107">
         <v>42.69</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="12"/>
-      <c r="B108" s="14" t="s">
+      <c r="A108" s="13"/>
+      <c r="B108" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C108" s="13">
-        <v>2930833333.3299999</v>
-      </c>
-      <c r="D108" s="13">
+      <c r="C108" s="2">
+        <v>2930833333</v>
+      </c>
+      <c r="D108">
         <v>150</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="12"/>
-      <c r="B109" s="14" t="s">
+      <c r="A109" s="13"/>
+      <c r="B109" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C109" s="13">
-        <v>108892249.7716206</v>
-      </c>
-      <c r="D109" s="13">
+      <c r="C109" s="2">
+        <v>198500000</v>
+      </c>
+      <c r="D109">
         <v>20.52</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -12658,6 +12617,26 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC3AB8D-448B-4BC5-89B4-998695B2552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89486067-0CA3-4462-89DC-4E65E91C57C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="67065" yWindow="-5580" windowWidth="38670" windowHeight="21150" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -821,9 +821,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31FF74EF-7037-4139-88AF-F295C305C1F7}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -839,7 +839,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -847,7 +847,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -863,25 +863,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185AF38-42FD-4CFF-B287-2FCFFF6C6EF3}">
   <dimension ref="A1:U28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" customWidth="1"/>
-    <col min="4" max="5" width="37.28515625" customWidth="1"/>
-    <col min="6" max="6" width="29.85546875" customWidth="1"/>
-    <col min="7" max="7" width="39.85546875" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" customWidth="1"/>
-    <col min="10" max="11" width="22.5703125" customWidth="1"/>
-    <col min="12" max="12" width="24.140625" customWidth="1"/>
-    <col min="13" max="13" width="27.7109375" customWidth="1"/>
-    <col min="14" max="14" width="22.85546875" customWidth="1"/>
-    <col min="15" max="16" width="20.140625" customWidth="1"/>
-    <col min="18" max="18" width="32.7109375" customWidth="1"/>
-    <col min="19" max="19" width="35.28515625" customWidth="1"/>
-    <col min="20" max="20" width="31.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="29.88671875" customWidth="1"/>
+    <col min="7" max="7" width="39.88671875" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="10" max="11" width="22.5546875" customWidth="1"/>
+    <col min="12" max="12" width="24.109375" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" customWidth="1"/>
+    <col min="14" max="14" width="22.88671875" customWidth="1"/>
+    <col min="15" max="16" width="20.109375" customWidth="1"/>
+    <col min="18" max="18" width="32.6640625" customWidth="1"/>
+    <col min="19" max="19" width="35.33203125" customWidth="1"/>
+    <col min="20" max="20" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -946,7 +946,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -2710,64 +2710,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0D039F-A3AA-471E-A6A2-F25F8348E84D}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
     </row>
   </sheetData>
@@ -2778,12 +2778,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6341E4C-4AB4-44A4-8119-B6BB3BEB6E84}">
   <dimension ref="A1:F325"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>3</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>4</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>5</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>6</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>7</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>8</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>9</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>10</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>11</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>12</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>4</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>5</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>6</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>7</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>8</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>9</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>10</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>11</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>12</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>4</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>5</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>6</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>7</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>8</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>9</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>10</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>11</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>12</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>3</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>5</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>6</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>7</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>8</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>9</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>10</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>11</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>12</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>3</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>4</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>5</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>6</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>7</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>8</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>9</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>10</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>11</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>12</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>2</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>3</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>4</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>5</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>6</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>7</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>8</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>9</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>10</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>11</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>12</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>2</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>3</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>4</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>5</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>6</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>7</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>8</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>9</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>10</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>11</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>3</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>4</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>5</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>6</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>7</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>8</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>9</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>10</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>11</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>12</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>2</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>3</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>4</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>5</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>6</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>7</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>8</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>9</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>10</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>11</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>12</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>1</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>2</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>3</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>4</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>5</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>6</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>7</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>8</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>9</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>10</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>11</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>12</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>1</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>2</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>3</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>4</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>5</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>6</v>
       </c>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>7</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>8</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>9</v>
       </c>
@@ -5623,7 +5623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>10</v>
       </c>
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>11</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>12</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>1</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>2</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>3</v>
       </c>
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>4</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>5</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>6</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>7</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>8</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>9</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>10</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>11</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>12</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>1</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>2</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>3</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>4</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>5</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>6</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>7</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>8</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>9</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>10</v>
       </c>
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>11</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>12</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>1</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>2</v>
       </c>
@@ -6203,7 +6203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>3</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>4</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>5</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>6</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>7</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>8</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>9</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>10</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>11</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>12</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>1</v>
       </c>
@@ -6423,7 +6423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>2</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>3</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>4</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>5</v>
       </c>
@@ -6503,7 +6503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>6</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>7</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>8</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>9</v>
       </c>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>10</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>11</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>12</v>
       </c>
@@ -6643,7 +6643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>1</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>2</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>3</v>
       </c>
@@ -6703,7 +6703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>4</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>5</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>6</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>7</v>
       </c>
@@ -6783,7 +6783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>8</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>9</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>10</v>
       </c>
@@ -6843,7 +6843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>11</v>
       </c>
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>12</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>1</v>
       </c>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>2</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>3</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>4</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>5</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>6</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>7</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>8</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>9</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>10</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>11</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>12</v>
       </c>
@@ -7123,7 +7123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>1</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>2</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>3</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>4</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>5</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>6</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>7</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>8</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>9</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>10</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>11</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>12</v>
       </c>
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>1</v>
       </c>
@@ -7383,7 +7383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>2</v>
       </c>
@@ -7403,7 +7403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>3</v>
       </c>
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>4</v>
       </c>
@@ -7443,7 +7443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>5</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>6</v>
       </c>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>7</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>8</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>9</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>10</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>11</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>12</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>1</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>2</v>
       </c>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>3</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>4</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>5</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>6</v>
       </c>
@@ -7723,7 +7723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>7</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>8</v>
       </c>
@@ -7763,7 +7763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>9</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>10</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>11</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>12</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>1</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>2</v>
       </c>
@@ -7883,7 +7883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>3</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>4</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>5</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>6</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>7</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>8</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>9</v>
       </c>
@@ -8023,7 +8023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>10</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>11</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>12</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>1</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>2</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>3</v>
       </c>
@@ -8143,7 +8143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>4</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>5</v>
       </c>
@@ -8183,7 +8183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>6</v>
       </c>
@@ -8203,7 +8203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>7</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>8</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>9</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>10</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>11</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>12</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>1</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>2</v>
       </c>
@@ -8363,7 +8363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>3</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>4</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>5</v>
       </c>
@@ -8423,7 +8423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>6</v>
       </c>
@@ -8443,7 +8443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>7</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>8</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>9</v>
       </c>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>10</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>11</v>
       </c>
@@ -8543,7 +8543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>12</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>1</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>2</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>3</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>4</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>5</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>6</v>
       </c>
@@ -8683,7 +8683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>7</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>8</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>9</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>10</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>11</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>12</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>1</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>2</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>3</v>
       </c>
@@ -8863,7 +8863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>4</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>5</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>6</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>7</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>8</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>9</v>
       </c>
@@ -8983,7 +8983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>10</v>
       </c>
@@ -9003,7 +9003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>11</v>
       </c>
@@ -9023,7 +9023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>12</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>1</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>2</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>3</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>4</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>5</v>
       </c>
@@ -9143,7 +9143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>6</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>7</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>8</v>
       </c>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>9</v>
       </c>
@@ -9223,7 +9223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>10</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>11</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>12</v>
       </c>
@@ -9291,20 +9291,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71493739-45C2-4A8D-9266-24BB3FC8F4DB}">
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" customWidth="1"/>
-    <col min="14" max="14" width="20.140625" customWidth="1"/>
-    <col min="20" max="20" width="20.5703125" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" customWidth="1"/>
+    <col min="10" max="10" width="21.88671875" customWidth="1"/>
+    <col min="14" max="14" width="20.109375" customWidth="1"/>
+    <col min="20" max="20" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -9419,7 +9419,7 @@
         <v>0.2</v>
       </c>
       <c r="K2" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L2" s="5">
         <v>0.8</v>
@@ -9470,7 +9470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>0.2</v>
       </c>
       <c r="K3" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L3" s="5">
         <v>0.8</v>
@@ -9553,7 +9553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>0.2</v>
       </c>
       <c r="K4" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L4" s="5">
         <v>0.8</v>
@@ -9636,7 +9636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>56</v>
       </c>
@@ -9668,7 +9668,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L5" s="5">
         <v>0.8</v>
@@ -9719,43 +9719,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
     </row>
   </sheetData>
@@ -9767,9 +9767,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69FD329D-454B-4A8C-B502-49D79ABB4242}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -9803,7 +9803,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -9820,7 +9820,7 @@
         <v>2.2200000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>2.4400000000000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>2.6599999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -9905,7 +9905,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>3.5400000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -9939,7 +9939,7 @@
         <v>3.7600000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -9990,7 +9990,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10007,7 +10007,7 @@
         <v>4.4200000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10024,7 +10024,7 @@
         <v>4.6399999999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -10041,7 +10041,7 @@
         <v>4.8599999999999997E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -10058,7 +10058,7 @@
         <v>5.0799999999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>5.5199999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -10109,7 +10109,7 @@
         <v>5.74E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>5.96E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>6.1800000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -10160,7 +10160,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -10177,7 +10177,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>6.8400000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10211,7 +10211,7 @@
         <v>7.0599999999999996E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -10228,7 +10228,7 @@
         <v>7.2800000000000004E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10253,9 +10253,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1143316B-9FC2-4B52-982D-1F4DD6859A8E}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -10289,7 +10289,7 @@
         <v>26229.707720000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -10306,7 +10306,7 @@
         <v>26589.174669999997</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -10323,7 +10323,7 @@
         <v>60431.69513</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -10340,7 +10340,7 @@
         <v>95314.195130000007</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -10357,7 +10357,7 @@
         <v>130196.6951</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>165780.465</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -10391,7 +10391,7 @@
         <v>179750.54879999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -10408,7 +10408,7 @@
         <v>195610.7611</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>196499.72339999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>198853.9976</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>202089.00579999998</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -10476,7 +10476,7 @@
         <v>164077.8836</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10493,7 +10493,7 @@
         <v>126654.49769999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>90701.344779999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>57298.538379999998</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -10544,7 +10544,7 @@
         <v>40938.322699999997</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -10561,7 +10561,7 @@
         <v>30788.296410000003</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -10578,7 +10578,7 @@
         <v>28368.054080000002</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -10595,7 +10595,7 @@
         <v>31250.81408</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -10612,7 +10612,7 @@
         <v>34011.350160000002</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -10629,7 +10629,7 @@
         <v>35066.675019999995</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>33453.543590000001</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -10663,7 +10663,7 @@
         <v>25310.301890000002</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>11877.08452</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10697,7 +10697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10739,9 +10739,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790A601-26C3-4DCA-97B6-9342C547A4A0}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -10775,7 +10775,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -10809,7 +10809,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -10843,7 +10843,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -10860,7 +10860,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -10877,7 +10877,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -10928,7 +10928,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -10962,7 +10962,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10979,7 +10979,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10996,7 +10996,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -11013,7 +11013,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -11030,7 +11030,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -11047,7 +11047,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -11081,7 +11081,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -11098,7 +11098,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -11115,7 +11115,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -11132,7 +11132,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -11149,7 +11149,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -11200,7 +11200,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -11225,14 +11225,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}">
   <dimension ref="A1:G109"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>68</v>
       </c>
@@ -11249,7 +11249,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="13">
         <v>2024</v>
       </c>
@@ -11266,7 +11266,7 @@
         <v>6.9372000000000003E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
       <c r="B3" s="12" t="s">
         <v>71</v>
@@ -11282,7 +11282,7 @@
         <v>4.9157999999999993E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13"/>
       <c r="B4" s="12" t="s">
         <v>72</v>
@@ -11297,7 +11297,7 @@
         <v>4.4639999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13"/>
       <c r="B5" s="12" t="s">
         <v>69</v>
@@ -11309,7 +11309,7 @@
         <v>22.68</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13">
         <v>2025</v>
       </c>
@@ -11323,7 +11323,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="13"/>
       <c r="B7" s="12" t="s">
         <v>71</v>
@@ -11335,7 +11335,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="12" t="s">
         <v>72</v>
@@ -11347,7 +11347,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="12" t="s">
         <v>69</v>
@@ -11360,7 +11360,7 @@
         <v>22.545000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>2026</v>
       </c>
@@ -11374,7 +11374,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="12" t="s">
         <v>71</v>
@@ -11386,7 +11386,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="12" t="s">
         <v>72</v>
@@ -11398,7 +11398,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="12" t="s">
         <v>69</v>
@@ -11411,7 +11411,7 @@
         <v>22.41</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>2027</v>
       </c>
@@ -11425,7 +11425,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="12" t="s">
         <v>71</v>
@@ -11437,7 +11437,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="12" t="s">
         <v>72</v>
@@ -11449,7 +11449,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="12" t="s">
         <v>69</v>
@@ -11462,7 +11462,7 @@
         <v>22.274999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>2028</v>
       </c>
@@ -11476,7 +11476,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="12" t="s">
         <v>71</v>
@@ -11488,7 +11488,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="12" t="s">
         <v>72</v>
@@ -11500,7 +11500,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="12" t="s">
         <v>69</v>
@@ -11513,7 +11513,7 @@
         <v>22.14</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>2029</v>
       </c>
@@ -11527,7 +11527,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="12" t="s">
         <v>71</v>
@@ -11539,7 +11539,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="12" t="s">
         <v>72</v>
@@ -11551,7 +11551,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="12" t="s">
         <v>69</v>
@@ -11564,7 +11564,7 @@
         <v>22.004999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
         <v>2030</v>
       </c>
@@ -11578,7 +11578,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="12" t="s">
         <v>71</v>
@@ -11590,7 +11590,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="12" t="s">
         <v>72</v>
@@ -11602,7 +11602,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="12" t="s">
         <v>69</v>
@@ -11615,7 +11615,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <v>2031</v>
       </c>
@@ -11629,7 +11629,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>
       <c r="B31" s="12" t="s">
         <v>71</v>
@@ -11641,7 +11641,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>
       <c r="B32" s="12" t="s">
         <v>72</v>
@@ -11653,7 +11653,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="12" t="s">
         <v>69</v>
@@ -11666,7 +11666,7 @@
         <v>21.734999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
         <v>2032</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="12" t="s">
         <v>71</v>
@@ -11692,7 +11692,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
       <c r="B36" s="12" t="s">
         <v>72</v>
@@ -11704,7 +11704,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37" s="12" t="s">
         <v>69</v>
@@ -11717,7 +11717,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
         <v>2033</v>
       </c>
@@ -11731,7 +11731,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="12" t="s">
         <v>71</v>
@@ -11743,7 +11743,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>
       <c r="B40" s="12" t="s">
         <v>72</v>
@@ -11755,7 +11755,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="12" t="s">
         <v>69</v>
@@ -11768,7 +11768,7 @@
         <v>21.465</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13">
         <v>2034</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="12" t="s">
         <v>71</v>
@@ -11794,7 +11794,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>
       <c r="B44" s="12" t="s">
         <v>72</v>
@@ -11806,7 +11806,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
       <c r="B45" s="12" t="s">
         <v>69</v>
@@ -11819,7 +11819,7 @@
         <v>21.33</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="13">
         <v>2035</v>
       </c>
@@ -11833,7 +11833,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
       <c r="B47" s="12" t="s">
         <v>71</v>
@@ -11845,7 +11845,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
       <c r="B48" s="12" t="s">
         <v>72</v>
@@ -11857,7 +11857,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
       <c r="B49" s="12" t="s">
         <v>69</v>
@@ -11870,7 +11870,7 @@
         <v>21.195</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="13">
         <v>2036</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="12" t="s">
         <v>71</v>
@@ -11896,7 +11896,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
       <c r="B52" s="12" t="s">
         <v>72</v>
@@ -11908,7 +11908,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
       <c r="B53" s="12" t="s">
         <v>69</v>
@@ -11921,7 +11921,7 @@
         <v>21.06</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="13">
         <v>2037</v>
       </c>
@@ -11935,7 +11935,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
       <c r="B55" s="12" t="s">
         <v>71</v>
@@ -11947,7 +11947,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
       <c r="B56" s="12" t="s">
         <v>72</v>
@@ -11959,7 +11959,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
       <c r="B57" s="12" t="s">
         <v>69</v>
@@ -11972,7 +11972,7 @@
         <v>20.925000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="13">
         <v>2038</v>
       </c>
@@ -11986,7 +11986,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
       <c r="B59" s="12" t="s">
         <v>71</v>
@@ -11998,7 +11998,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
       <c r="B60" s="12" t="s">
         <v>72</v>
@@ -12010,7 +12010,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="12" t="s">
         <v>69</v>
@@ -12023,7 +12023,7 @@
         <v>20.79</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="13">
         <v>2039</v>
       </c>
@@ -12037,7 +12037,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>
       <c r="B63" s="12" t="s">
         <v>71</v>
@@ -12049,7 +12049,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>
       <c r="B64" s="12" t="s">
         <v>72</v>
@@ -12061,7 +12061,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="13"/>
       <c r="B65" s="12" t="s">
         <v>69</v>
@@ -12074,7 +12074,7 @@
         <v>20.655000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="13">
         <v>2040</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
       <c r="B67" s="12" t="s">
         <v>71</v>
@@ -12100,7 +12100,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
       <c r="B68" s="12" t="s">
         <v>72</v>
@@ -12112,7 +12112,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="13"/>
       <c r="B69" s="12" t="s">
         <v>69</v>
@@ -12125,7 +12125,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="13">
         <v>2041</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
       <c r="B71" s="12" t="s">
         <v>71</v>
@@ -12151,7 +12151,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>
       <c r="B72" s="12" t="s">
         <v>72</v>
@@ -12163,7 +12163,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>
       <c r="B73" s="12" t="s">
         <v>69</v>
@@ -12176,7 +12176,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="13">
         <v>2042</v>
       </c>
@@ -12190,7 +12190,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>
       <c r="B75" s="12" t="s">
         <v>71</v>
@@ -12202,7 +12202,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>
       <c r="B76" s="12" t="s">
         <v>72</v>
@@ -12214,7 +12214,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="13"/>
       <c r="B77" s="12" t="s">
         <v>69</v>
@@ -12227,7 +12227,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="13">
         <v>2043</v>
       </c>
@@ -12241,7 +12241,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="13"/>
       <c r="B79" s="12" t="s">
         <v>71</v>
@@ -12253,7 +12253,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="13"/>
       <c r="B80" s="12" t="s">
         <v>72</v>
@@ -12265,7 +12265,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="13"/>
       <c r="B81" s="12" t="s">
         <v>69</v>
@@ -12278,7 +12278,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="13">
         <v>2044</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="13"/>
       <c r="B83" s="12" t="s">
         <v>71</v>
@@ -12304,7 +12304,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="13"/>
       <c r="B84" s="12" t="s">
         <v>72</v>
@@ -12316,7 +12316,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="13"/>
       <c r="B85" s="12" t="s">
         <v>69</v>
@@ -12329,7 +12329,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="13">
         <v>2045</v>
       </c>
@@ -12343,7 +12343,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="13"/>
       <c r="B87" s="12" t="s">
         <v>71</v>
@@ -12355,7 +12355,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="13"/>
       <c r="B88" s="12" t="s">
         <v>72</v>
@@ -12367,7 +12367,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="13"/>
       <c r="B89" s="12" t="s">
         <v>69</v>
@@ -12380,7 +12380,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="13">
         <v>2046</v>
       </c>
@@ -12394,7 +12394,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="13"/>
       <c r="B91" s="12" t="s">
         <v>71</v>
@@ -12406,7 +12406,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="13"/>
       <c r="B92" s="12" t="s">
         <v>72</v>
@@ -12418,7 +12418,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="13"/>
       <c r="B93" s="12" t="s">
         <v>69</v>
@@ -12431,7 +12431,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="13">
         <v>2047</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="13"/>
       <c r="B95" s="12" t="s">
         <v>71</v>
@@ -12457,7 +12457,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="13"/>
       <c r="B96" s="12" t="s">
         <v>72</v>
@@ -12469,7 +12469,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="13"/>
       <c r="B97" s="12" t="s">
         <v>69</v>
@@ -12482,7 +12482,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="13">
         <v>2048</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="13"/>
       <c r="B99" s="12" t="s">
         <v>71</v>
@@ -12508,7 +12508,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="13"/>
       <c r="B100" s="12" t="s">
         <v>72</v>
@@ -12520,7 +12520,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="13"/>
       <c r="B101" s="12" t="s">
         <v>69</v>
@@ -12533,7 +12533,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="13">
         <v>2049</v>
       </c>
@@ -12547,7 +12547,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="13"/>
       <c r="B103" s="12" t="s">
         <v>71</v>
@@ -12559,7 +12559,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="13"/>
       <c r="B104" s="12" t="s">
         <v>72</v>
@@ -12571,7 +12571,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="13"/>
       <c r="B105" s="12" t="s">
         <v>69</v>
@@ -12584,7 +12584,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="13">
         <v>2050</v>
       </c>
@@ -12598,7 +12598,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="13"/>
       <c r="B107" s="12" t="s">
         <v>71</v>
@@ -12610,7 +12610,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="13"/>
       <c r="B108" s="12" t="s">
         <v>72</v>
@@ -12622,7 +12622,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="13"/>
       <c r="B109" s="12" t="s">
         <v>69</v>
@@ -12638,6 +12638,26 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -12645,26 +12665,6 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
